--- a/data/final_tables /Table_S7.xlsx
+++ b/data/final_tables /Table_S7.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anthonyfuentes/Desktop/Submission/data/geochronology/final_tables/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anthonyfuentes/GitHub/Sed_Hematite_UPb/data/final_tables /"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CFD9FEC-6C26-FE4B-A67E-B8D900D3D68D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5341ECD7-4494-224A-AD6B-4A8D17BFF96E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{983A3024-F279-4749-8013-AF771CBD574B}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{983A3024-F279-4749-8013-AF771CBD574B}"/>
   </bookViews>
   <sheets>
     <sheet name="U_Pb_data" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">U_Pb_data!$A$1:$Q$407</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -2195,7 +2198,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2264,16 +2267,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2652,7 +2645,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L506"/>
+  <dimension ref="A1:L504"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="18.28515625" style="1" customWidth="1"/>
@@ -17899,1369 +17892,1367 @@
         <v>0.96010838899999995</v>
       </c>
     </row>
-    <row r="408" spans="1:12" s="29" customFormat="1">
-      <c r="A408" s="26"/>
-      <c r="B408" s="27"/>
-      <c r="C408" s="28"/>
-      <c r="D408" s="28"/>
-      <c r="E408" s="28"/>
-      <c r="F408" s="28"/>
-      <c r="G408" s="28"/>
-      <c r="H408" s="28"/>
-      <c r="I408" s="28"/>
-      <c r="J408" s="28"/>
-      <c r="K408" s="28"/>
-      <c r="L408" s="28"/>
-    </row>
-    <row r="409" spans="1:12" s="29" customFormat="1">
-      <c r="A409" s="26"/>
-      <c r="B409" s="27"/>
-      <c r="C409" s="28"/>
-      <c r="D409" s="28"/>
-      <c r="E409" s="28"/>
-      <c r="F409" s="28"/>
-      <c r="G409" s="28"/>
-      <c r="H409" s="28"/>
-      <c r="I409" s="28"/>
-      <c r="J409" s="28"/>
-      <c r="K409" s="28"/>
-      <c r="L409" s="28"/>
-    </row>
-    <row r="410" spans="1:12" s="29" customFormat="1">
-      <c r="A410" s="26"/>
-      <c r="B410" s="27"/>
-      <c r="C410" s="28"/>
-      <c r="D410" s="28"/>
-      <c r="E410" s="28"/>
-      <c r="F410" s="28"/>
-      <c r="G410" s="28"/>
-      <c r="H410" s="28"/>
-      <c r="I410" s="28"/>
-      <c r="J410" s="28"/>
-      <c r="K410" s="28"/>
-      <c r="L410" s="28"/>
-    </row>
-    <row r="411" spans="1:12" s="29" customFormat="1">
-      <c r="A411" s="26"/>
-      <c r="B411" s="27"/>
-      <c r="C411" s="28"/>
-      <c r="D411" s="28"/>
-      <c r="E411" s="28"/>
-      <c r="F411" s="28"/>
-      <c r="G411" s="28"/>
-      <c r="H411" s="28"/>
-      <c r="I411" s="28"/>
-      <c r="J411" s="28"/>
-      <c r="K411" s="28"/>
-      <c r="L411" s="28"/>
-    </row>
-    <row r="412" spans="1:12" s="29" customFormat="1">
-      <c r="A412" s="26"/>
-      <c r="B412" s="27"/>
-      <c r="C412" s="28"/>
-      <c r="D412" s="28"/>
-      <c r="E412" s="28"/>
-      <c r="F412" s="28"/>
-      <c r="G412" s="28"/>
-      <c r="H412" s="28"/>
-      <c r="I412" s="28"/>
-      <c r="J412" s="28"/>
-      <c r="K412" s="28"/>
-      <c r="L412" s="28"/>
-    </row>
-    <row r="413" spans="1:12" s="29" customFormat="1">
-      <c r="A413" s="26"/>
-      <c r="B413" s="27"/>
-      <c r="C413" s="28"/>
-      <c r="D413" s="28"/>
-      <c r="E413" s="28"/>
-      <c r="F413" s="28"/>
-      <c r="G413" s="28"/>
-      <c r="H413" s="28"/>
-      <c r="I413" s="28"/>
-      <c r="J413" s="28"/>
-      <c r="K413" s="28"/>
-      <c r="L413" s="28"/>
-    </row>
-    <row r="414" spans="1:12" s="29" customFormat="1">
-      <c r="A414" s="26"/>
-      <c r="B414" s="27"/>
-      <c r="C414" s="28"/>
-      <c r="D414" s="28"/>
-      <c r="E414" s="28"/>
-      <c r="F414" s="28"/>
-      <c r="G414" s="28"/>
-      <c r="H414" s="28"/>
-      <c r="I414" s="28"/>
-      <c r="J414" s="28"/>
-      <c r="K414" s="28"/>
-      <c r="L414" s="28"/>
-    </row>
-    <row r="415" spans="1:12" s="29" customFormat="1">
-      <c r="A415" s="26"/>
-      <c r="B415" s="27"/>
-      <c r="C415" s="28"/>
-      <c r="D415" s="28"/>
-      <c r="E415" s="28"/>
-      <c r="F415" s="28"/>
-      <c r="G415" s="28"/>
-      <c r="H415" s="28"/>
-      <c r="I415" s="28"/>
-      <c r="J415" s="28"/>
-      <c r="K415" s="28"/>
-      <c r="L415" s="28"/>
-    </row>
-    <row r="416" spans="1:12" s="29" customFormat="1">
-      <c r="A416" s="26"/>
-      <c r="B416" s="27"/>
-      <c r="C416" s="28"/>
-      <c r="D416" s="28"/>
-      <c r="E416" s="28"/>
-      <c r="F416" s="28"/>
-      <c r="G416" s="28"/>
-      <c r="H416" s="28"/>
-      <c r="I416" s="28"/>
-      <c r="J416" s="28"/>
-      <c r="K416" s="28"/>
-      <c r="L416" s="28"/>
-    </row>
-    <row r="417" spans="1:12" s="29" customFormat="1">
-      <c r="A417" s="26"/>
-      <c r="B417" s="27"/>
-      <c r="C417" s="28"/>
-      <c r="D417" s="28"/>
-      <c r="E417" s="28"/>
-      <c r="F417" s="28"/>
-      <c r="G417" s="28"/>
-      <c r="H417" s="28"/>
-      <c r="I417" s="28"/>
-      <c r="J417" s="28"/>
-      <c r="K417" s="28"/>
-      <c r="L417" s="28"/>
-    </row>
-    <row r="418" spans="1:12" s="29" customFormat="1">
-      <c r="A418" s="26"/>
-      <c r="B418" s="27"/>
-      <c r="C418" s="28"/>
-      <c r="D418" s="28"/>
-      <c r="E418" s="28"/>
-      <c r="F418" s="28"/>
-      <c r="G418" s="28"/>
-      <c r="H418" s="28"/>
-      <c r="I418" s="28"/>
-      <c r="J418" s="28"/>
-      <c r="K418" s="28"/>
-      <c r="L418" s="28"/>
-    </row>
-    <row r="419" spans="1:12" s="29" customFormat="1">
-      <c r="A419" s="26"/>
-      <c r="B419" s="27"/>
-      <c r="C419" s="28"/>
-      <c r="D419" s="28"/>
-      <c r="E419" s="28"/>
-      <c r="F419" s="28"/>
-      <c r="G419" s="28"/>
-      <c r="H419" s="28"/>
-      <c r="I419" s="28"/>
-      <c r="J419" s="28"/>
-      <c r="K419" s="28"/>
-      <c r="L419" s="28"/>
-    </row>
-    <row r="420" spans="1:12" s="29" customFormat="1">
-      <c r="A420" s="26"/>
-      <c r="B420" s="27"/>
-      <c r="C420" s="28"/>
-      <c r="D420" s="28"/>
-      <c r="E420" s="28"/>
-      <c r="F420" s="28"/>
-      <c r="G420" s="28"/>
-      <c r="H420" s="28"/>
-      <c r="I420" s="28"/>
-      <c r="J420" s="28"/>
-      <c r="K420" s="28"/>
-      <c r="L420" s="28"/>
-    </row>
-    <row r="421" spans="1:12" s="29" customFormat="1">
-      <c r="A421" s="26"/>
-      <c r="B421" s="27"/>
-      <c r="C421" s="28"/>
-      <c r="D421" s="28"/>
-      <c r="E421" s="28"/>
-      <c r="F421" s="28"/>
-      <c r="G421" s="28"/>
-      <c r="H421" s="28"/>
-      <c r="I421" s="28"/>
-      <c r="J421" s="28"/>
-      <c r="K421" s="28"/>
-      <c r="L421" s="28"/>
-    </row>
-    <row r="422" spans="1:12" s="29" customFormat="1">
-      <c r="A422" s="26"/>
-      <c r="B422" s="27"/>
-      <c r="C422" s="28"/>
-      <c r="D422" s="28"/>
-      <c r="E422" s="28"/>
-      <c r="F422" s="28"/>
-      <c r="G422" s="28"/>
-      <c r="H422" s="28"/>
-      <c r="I422" s="28"/>
-      <c r="J422" s="28"/>
-      <c r="K422" s="28"/>
-      <c r="L422" s="28"/>
-    </row>
-    <row r="423" spans="1:12" s="29" customFormat="1">
-      <c r="A423" s="26"/>
-      <c r="B423" s="27"/>
-      <c r="C423" s="28"/>
-      <c r="D423" s="28"/>
-      <c r="E423" s="28"/>
-      <c r="F423" s="28"/>
-      <c r="G423" s="28"/>
-      <c r="H423" s="28"/>
-      <c r="I423" s="28"/>
-      <c r="J423" s="28"/>
-      <c r="K423" s="28"/>
-      <c r="L423" s="28"/>
-    </row>
-    <row r="424" spans="1:12" s="29" customFormat="1">
-      <c r="A424" s="26"/>
-      <c r="B424" s="27"/>
-      <c r="C424" s="28"/>
-      <c r="D424" s="28"/>
-      <c r="E424" s="28"/>
-      <c r="F424" s="28"/>
-      <c r="G424" s="28"/>
-      <c r="H424" s="28"/>
-      <c r="I424" s="28"/>
-      <c r="J424" s="28"/>
-      <c r="K424" s="28"/>
-      <c r="L424" s="28"/>
-    </row>
-    <row r="425" spans="1:12" s="29" customFormat="1">
-      <c r="A425" s="26"/>
-      <c r="B425" s="27"/>
-      <c r="C425" s="28"/>
-      <c r="D425" s="28"/>
-      <c r="E425" s="28"/>
-      <c r="F425" s="28"/>
-      <c r="G425" s="28"/>
-      <c r="H425" s="28"/>
-      <c r="I425" s="28"/>
-      <c r="J425" s="28"/>
-      <c r="K425" s="28"/>
-      <c r="L425" s="28"/>
-    </row>
-    <row r="426" spans="1:12" s="29" customFormat="1">
-      <c r="A426" s="26"/>
-      <c r="B426" s="27"/>
-      <c r="C426" s="28"/>
-      <c r="D426" s="28"/>
-      <c r="E426" s="28"/>
-      <c r="F426" s="28"/>
-      <c r="G426" s="28"/>
-      <c r="H426" s="28"/>
-      <c r="I426" s="28"/>
-      <c r="J426" s="28"/>
-      <c r="K426" s="28"/>
-      <c r="L426" s="28"/>
-    </row>
-    <row r="427" spans="1:12" s="29" customFormat="1">
-      <c r="A427" s="26"/>
-      <c r="B427" s="27"/>
-      <c r="C427" s="28"/>
-      <c r="D427" s="28"/>
-      <c r="E427" s="28"/>
-      <c r="F427" s="28"/>
-      <c r="G427" s="28"/>
-      <c r="H427" s="28"/>
-      <c r="I427" s="28"/>
-      <c r="J427" s="28"/>
-      <c r="K427" s="28"/>
-      <c r="L427" s="28"/>
-    </row>
-    <row r="428" spans="1:12" s="29" customFormat="1">
-      <c r="A428" s="26"/>
-      <c r="B428" s="27"/>
-      <c r="C428" s="28"/>
-      <c r="D428" s="28"/>
-      <c r="E428" s="28"/>
-      <c r="F428" s="28"/>
-      <c r="G428" s="28"/>
-      <c r="H428" s="28"/>
-      <c r="I428" s="28"/>
-      <c r="J428" s="28"/>
-      <c r="K428" s="28"/>
-      <c r="L428" s="28"/>
-    </row>
-    <row r="429" spans="1:12" s="29" customFormat="1">
-      <c r="A429" s="26"/>
-      <c r="B429" s="27"/>
-      <c r="C429" s="28"/>
-      <c r="D429" s="28"/>
-      <c r="E429" s="28"/>
-      <c r="F429" s="28"/>
-      <c r="G429" s="28"/>
-      <c r="H429" s="28"/>
-      <c r="I429" s="28"/>
-      <c r="J429" s="28"/>
-      <c r="K429" s="28"/>
-      <c r="L429" s="28"/>
-    </row>
-    <row r="430" spans="1:12" s="29" customFormat="1">
-      <c r="A430" s="26"/>
-      <c r="B430" s="27"/>
-      <c r="C430" s="28"/>
-      <c r="D430" s="28"/>
-      <c r="E430" s="28"/>
-      <c r="F430" s="28"/>
-      <c r="G430" s="28"/>
-      <c r="H430" s="28"/>
-      <c r="I430" s="28"/>
-      <c r="J430" s="28"/>
-      <c r="K430" s="28"/>
-      <c r="L430" s="28"/>
-    </row>
-    <row r="431" spans="1:12" s="29" customFormat="1">
-      <c r="A431" s="26"/>
-      <c r="B431" s="27"/>
-      <c r="C431" s="28"/>
-      <c r="D431" s="28"/>
-      <c r="E431" s="28"/>
-      <c r="F431" s="28"/>
-      <c r="G431" s="28"/>
-      <c r="H431" s="28"/>
-      <c r="I431" s="28"/>
-      <c r="J431" s="28"/>
-      <c r="K431" s="28"/>
-      <c r="L431" s="28"/>
-    </row>
-    <row r="432" spans="1:12" s="29" customFormat="1">
-      <c r="A432" s="26"/>
-      <c r="B432" s="27"/>
-      <c r="C432" s="28"/>
-      <c r="D432" s="28"/>
-      <c r="E432" s="28"/>
-      <c r="F432" s="28"/>
-      <c r="G432" s="28"/>
-      <c r="H432" s="28"/>
-      <c r="I432" s="28"/>
-      <c r="J432" s="28"/>
-      <c r="K432" s="28"/>
-      <c r="L432" s="28"/>
-    </row>
-    <row r="433" spans="1:12" s="29" customFormat="1">
-      <c r="A433" s="26"/>
-      <c r="B433" s="27"/>
-      <c r="C433" s="28"/>
-      <c r="D433" s="28"/>
-      <c r="E433" s="28"/>
-      <c r="F433" s="28"/>
-      <c r="G433" s="28"/>
-      <c r="H433" s="28"/>
-      <c r="I433" s="28"/>
-      <c r="J433" s="28"/>
-      <c r="K433" s="28"/>
-      <c r="L433" s="28"/>
-    </row>
-    <row r="434" spans="1:12" s="29" customFormat="1">
-      <c r="A434" s="26"/>
-      <c r="B434" s="27"/>
-      <c r="C434" s="28"/>
-      <c r="D434" s="28"/>
-      <c r="E434" s="28"/>
-      <c r="F434" s="28"/>
-      <c r="G434" s="28"/>
-      <c r="H434" s="28"/>
-      <c r="I434" s="28"/>
-      <c r="J434" s="28"/>
-      <c r="K434" s="28"/>
-      <c r="L434" s="28"/>
-    </row>
-    <row r="435" spans="1:12" s="29" customFormat="1">
-      <c r="A435" s="26"/>
-      <c r="B435" s="27"/>
-      <c r="C435" s="28"/>
-      <c r="D435" s="28"/>
-      <c r="E435" s="28"/>
-      <c r="F435" s="28"/>
-      <c r="G435" s="28"/>
-      <c r="H435" s="28"/>
-      <c r="I435" s="28"/>
-      <c r="J435" s="28"/>
-      <c r="K435" s="28"/>
-      <c r="L435" s="28"/>
-    </row>
-    <row r="436" spans="1:12" s="29" customFormat="1">
-      <c r="A436" s="26"/>
-      <c r="B436" s="27"/>
-      <c r="C436" s="28"/>
-      <c r="D436" s="28"/>
-      <c r="E436" s="28"/>
-      <c r="F436" s="28"/>
-      <c r="G436" s="28"/>
-      <c r="H436" s="28"/>
-      <c r="I436" s="28"/>
-      <c r="J436" s="28"/>
-      <c r="K436" s="28"/>
-      <c r="L436" s="28"/>
-    </row>
-    <row r="437" spans="1:12" s="29" customFormat="1">
-      <c r="A437" s="26"/>
-      <c r="B437" s="27"/>
-      <c r="C437" s="28"/>
-      <c r="D437" s="28"/>
-      <c r="E437" s="28"/>
-      <c r="F437" s="28"/>
-      <c r="G437" s="28"/>
-      <c r="H437" s="28"/>
-      <c r="I437" s="28"/>
-      <c r="J437" s="28"/>
-      <c r="K437" s="28"/>
-      <c r="L437" s="28"/>
-    </row>
-    <row r="438" spans="1:12" s="29" customFormat="1">
-      <c r="A438" s="26"/>
-      <c r="B438" s="27"/>
-      <c r="C438" s="28"/>
-      <c r="D438" s="28"/>
-      <c r="E438" s="28"/>
-      <c r="F438" s="28"/>
-      <c r="G438" s="28"/>
-      <c r="H438" s="28"/>
-      <c r="I438" s="28"/>
-      <c r="J438" s="28"/>
-      <c r="K438" s="28"/>
-      <c r="L438" s="28"/>
-    </row>
-    <row r="439" spans="1:12" s="29" customFormat="1">
-      <c r="A439" s="26"/>
-      <c r="B439" s="27"/>
-      <c r="C439" s="28"/>
-      <c r="D439" s="28"/>
-      <c r="E439" s="28"/>
-      <c r="F439" s="28"/>
-      <c r="G439" s="28"/>
-      <c r="H439" s="28"/>
-      <c r="I439" s="28"/>
-      <c r="J439" s="28"/>
-      <c r="K439" s="28"/>
-      <c r="L439" s="28"/>
-    </row>
-    <row r="440" spans="1:12" s="29" customFormat="1">
-      <c r="A440" s="26"/>
-      <c r="B440" s="27"/>
-      <c r="C440" s="28"/>
-      <c r="D440" s="28"/>
-      <c r="E440" s="28"/>
-      <c r="F440" s="28"/>
-      <c r="G440" s="28"/>
-      <c r="H440" s="28"/>
-      <c r="I440" s="28"/>
-      <c r="J440" s="28"/>
-      <c r="K440" s="28"/>
-      <c r="L440" s="28"/>
-    </row>
-    <row r="441" spans="1:12" s="29" customFormat="1">
-      <c r="A441" s="26"/>
-      <c r="B441" s="27"/>
-      <c r="C441" s="28"/>
-      <c r="D441" s="28"/>
-      <c r="E441" s="28"/>
-      <c r="F441" s="28"/>
-      <c r="G441" s="28"/>
-      <c r="H441" s="28"/>
-      <c r="I441" s="28"/>
-      <c r="J441" s="28"/>
-      <c r="K441" s="28"/>
-      <c r="L441" s="28"/>
-    </row>
-    <row r="442" spans="1:12" s="29" customFormat="1">
-      <c r="A442" s="26"/>
-      <c r="B442" s="27"/>
-      <c r="C442" s="28"/>
-      <c r="D442" s="28"/>
-      <c r="E442" s="28"/>
-      <c r="F442" s="28"/>
-      <c r="G442" s="28"/>
-      <c r="H442" s="28"/>
-      <c r="I442" s="28"/>
-      <c r="J442" s="28"/>
-      <c r="K442" s="28"/>
-      <c r="L442" s="28"/>
-    </row>
-    <row r="443" spans="1:12" s="29" customFormat="1">
-      <c r="A443" s="26"/>
-      <c r="B443" s="27"/>
-      <c r="C443" s="28"/>
-      <c r="D443" s="28"/>
-      <c r="E443" s="28"/>
-      <c r="F443" s="28"/>
-      <c r="G443" s="28"/>
-      <c r="H443" s="28"/>
-      <c r="I443" s="28"/>
-      <c r="J443" s="28"/>
-      <c r="K443" s="28"/>
-      <c r="L443" s="28"/>
-    </row>
-    <row r="444" spans="1:12" s="29" customFormat="1">
-      <c r="A444" s="26"/>
-      <c r="B444" s="27"/>
-      <c r="C444" s="28"/>
-      <c r="D444" s="28"/>
-      <c r="E444" s="28"/>
-      <c r="F444" s="28"/>
-      <c r="G444" s="28"/>
-      <c r="H444" s="28"/>
-      <c r="I444" s="28"/>
-      <c r="J444" s="28"/>
-      <c r="K444" s="28"/>
-      <c r="L444" s="28"/>
-    </row>
-    <row r="445" spans="1:12" s="29" customFormat="1">
-      <c r="A445" s="26"/>
-      <c r="B445" s="27"/>
-      <c r="C445" s="28"/>
-      <c r="D445" s="28"/>
-      <c r="E445" s="28"/>
-      <c r="F445" s="28"/>
-      <c r="G445" s="28"/>
-      <c r="H445" s="28"/>
-      <c r="I445" s="28"/>
-      <c r="J445" s="28"/>
-      <c r="K445" s="28"/>
-      <c r="L445" s="28"/>
-    </row>
-    <row r="446" spans="1:12" s="29" customFormat="1">
-      <c r="A446" s="26"/>
-      <c r="B446" s="27"/>
-      <c r="C446" s="28"/>
-      <c r="D446" s="28"/>
-      <c r="E446" s="28"/>
-      <c r="F446" s="28"/>
-      <c r="G446" s="28"/>
-      <c r="H446" s="28"/>
-      <c r="I446" s="28"/>
-      <c r="J446" s="28"/>
-      <c r="K446" s="28"/>
-      <c r="L446" s="28"/>
-    </row>
-    <row r="447" spans="1:12" s="29" customFormat="1">
-      <c r="A447" s="26"/>
-      <c r="B447" s="27"/>
-      <c r="C447" s="28"/>
-      <c r="D447" s="28"/>
-      <c r="E447" s="28"/>
-      <c r="F447" s="28"/>
-      <c r="G447" s="28"/>
-      <c r="H447" s="28"/>
-      <c r="I447" s="28"/>
-      <c r="J447" s="28"/>
-      <c r="K447" s="28"/>
-      <c r="L447" s="28"/>
-    </row>
-    <row r="448" spans="1:12" s="29" customFormat="1">
-      <c r="A448" s="26"/>
-      <c r="B448" s="27"/>
-      <c r="C448" s="28"/>
-      <c r="D448" s="28"/>
-      <c r="E448" s="28"/>
-      <c r="F448" s="28"/>
-      <c r="G448" s="28"/>
-      <c r="H448" s="28"/>
-      <c r="I448" s="28"/>
-      <c r="J448" s="28"/>
-      <c r="K448" s="28"/>
-      <c r="L448" s="28"/>
-    </row>
-    <row r="449" spans="1:12" s="29" customFormat="1">
-      <c r="A449" s="26"/>
-      <c r="B449" s="27"/>
-      <c r="C449" s="28"/>
-      <c r="D449" s="28"/>
-      <c r="E449" s="28"/>
-      <c r="F449" s="28"/>
-      <c r="G449" s="28"/>
-      <c r="H449" s="28"/>
-      <c r="I449" s="28"/>
-      <c r="J449" s="28"/>
-      <c r="K449" s="28"/>
-      <c r="L449" s="28"/>
-    </row>
-    <row r="450" spans="1:12" s="29" customFormat="1">
-      <c r="A450" s="26"/>
-      <c r="B450" s="27"/>
-      <c r="C450" s="28"/>
-      <c r="D450" s="28"/>
-      <c r="E450" s="28"/>
-      <c r="F450" s="28"/>
-      <c r="G450" s="28"/>
-      <c r="H450" s="28"/>
-      <c r="I450" s="28"/>
-      <c r="J450" s="28"/>
-      <c r="K450" s="28"/>
-      <c r="L450" s="28"/>
-    </row>
-    <row r="451" spans="1:12" s="29" customFormat="1">
-      <c r="A451" s="26"/>
-      <c r="B451" s="27"/>
-      <c r="C451" s="28"/>
-      <c r="D451" s="28"/>
-      <c r="E451" s="28"/>
-      <c r="F451" s="28"/>
-      <c r="G451" s="28"/>
-      <c r="H451" s="28"/>
-      <c r="I451" s="28"/>
-      <c r="J451" s="28"/>
-      <c r="K451" s="28"/>
-      <c r="L451" s="28"/>
-    </row>
-    <row r="452" spans="1:12" s="29" customFormat="1">
-      <c r="A452" s="26"/>
-      <c r="B452" s="27"/>
-      <c r="C452" s="28"/>
-      <c r="D452" s="28"/>
-      <c r="E452" s="28"/>
-      <c r="F452" s="28"/>
-      <c r="G452" s="28"/>
-      <c r="H452" s="28"/>
-      <c r="I452" s="28"/>
-      <c r="J452" s="28"/>
-      <c r="K452" s="28"/>
-      <c r="L452" s="28"/>
-    </row>
-    <row r="453" spans="1:12" s="29" customFormat="1">
-      <c r="A453" s="26"/>
-      <c r="B453" s="27"/>
-      <c r="C453" s="28"/>
-      <c r="D453" s="28"/>
-      <c r="E453" s="28"/>
-      <c r="F453" s="28"/>
-      <c r="G453" s="28"/>
-      <c r="H453" s="28"/>
-      <c r="I453" s="28"/>
-      <c r="J453" s="28"/>
-      <c r="K453" s="28"/>
-      <c r="L453" s="28"/>
-    </row>
-    <row r="454" spans="1:12" s="29" customFormat="1">
-      <c r="A454" s="26"/>
-      <c r="B454" s="27"/>
-      <c r="C454" s="28"/>
-      <c r="D454" s="28"/>
-      <c r="E454" s="28"/>
-      <c r="F454" s="28"/>
-      <c r="G454" s="28"/>
-      <c r="H454" s="28"/>
-      <c r="I454" s="28"/>
-      <c r="J454" s="28"/>
-      <c r="K454" s="28"/>
-      <c r="L454" s="28"/>
-    </row>
-    <row r="455" spans="1:12" s="29" customFormat="1">
-      <c r="A455" s="26"/>
-      <c r="B455" s="27"/>
-      <c r="C455" s="28"/>
-      <c r="D455" s="28"/>
-      <c r="E455" s="28"/>
-      <c r="F455" s="28"/>
-      <c r="G455" s="28"/>
-      <c r="H455" s="28"/>
-      <c r="I455" s="28"/>
-      <c r="J455" s="28"/>
-      <c r="K455" s="28"/>
-      <c r="L455" s="28"/>
-    </row>
-    <row r="456" spans="1:12" s="29" customFormat="1">
-      <c r="A456" s="26"/>
-      <c r="B456" s="27"/>
-      <c r="C456" s="28"/>
-      <c r="D456" s="28"/>
-      <c r="E456" s="28"/>
-      <c r="F456" s="28"/>
-      <c r="G456" s="28"/>
-      <c r="H456" s="28"/>
-      <c r="I456" s="28"/>
-      <c r="J456" s="28"/>
-      <c r="K456" s="28"/>
-      <c r="L456" s="28"/>
-    </row>
-    <row r="457" spans="1:12" s="29" customFormat="1">
-      <c r="A457" s="26"/>
-      <c r="B457" s="27"/>
-      <c r="C457" s="28"/>
-      <c r="D457" s="28"/>
-      <c r="E457" s="28"/>
-      <c r="F457" s="28"/>
-      <c r="G457" s="28"/>
-      <c r="H457" s="28"/>
-      <c r="I457" s="28"/>
-      <c r="J457" s="28"/>
-      <c r="K457" s="28"/>
-      <c r="L457" s="28"/>
-    </row>
-    <row r="458" spans="1:12" s="29" customFormat="1">
-      <c r="A458" s="26"/>
-      <c r="B458" s="27"/>
-      <c r="C458" s="28"/>
-      <c r="D458" s="28"/>
-      <c r="E458" s="28"/>
-      <c r="F458" s="28"/>
-      <c r="G458" s="28"/>
-      <c r="H458" s="28"/>
-      <c r="I458" s="28"/>
-      <c r="J458" s="28"/>
-      <c r="K458" s="28"/>
-      <c r="L458" s="28"/>
-    </row>
-    <row r="459" spans="1:12" s="29" customFormat="1">
-      <c r="A459" s="26"/>
-      <c r="B459" s="27"/>
-      <c r="C459" s="28"/>
-      <c r="D459" s="28"/>
-      <c r="E459" s="28"/>
-      <c r="F459" s="28"/>
-      <c r="G459" s="28"/>
-      <c r="H459" s="28"/>
-      <c r="I459" s="28"/>
-      <c r="J459" s="28"/>
-      <c r="K459" s="28"/>
-      <c r="L459" s="28"/>
-    </row>
-    <row r="460" spans="1:12" s="29" customFormat="1">
-      <c r="A460" s="26"/>
-      <c r="B460" s="27"/>
-      <c r="C460" s="28"/>
-      <c r="D460" s="28"/>
-      <c r="E460" s="28"/>
-      <c r="F460" s="28"/>
-      <c r="G460" s="28"/>
-      <c r="H460" s="28"/>
-      <c r="I460" s="28"/>
-      <c r="J460" s="28"/>
-      <c r="K460" s="28"/>
-      <c r="L460" s="28"/>
-    </row>
-    <row r="461" spans="1:12" s="29" customFormat="1">
-      <c r="A461" s="26"/>
-      <c r="B461" s="27"/>
-      <c r="C461" s="28"/>
-      <c r="D461" s="28"/>
-      <c r="E461" s="28"/>
-      <c r="F461" s="28"/>
-      <c r="G461" s="28"/>
-      <c r="H461" s="28"/>
-      <c r="I461" s="28"/>
-      <c r="J461" s="28"/>
-      <c r="K461" s="28"/>
-      <c r="L461" s="28"/>
-    </row>
-    <row r="462" spans="1:12" s="29" customFormat="1">
-      <c r="A462" s="26"/>
-      <c r="B462" s="27"/>
-      <c r="C462" s="28"/>
-      <c r="D462" s="28"/>
-      <c r="E462" s="28"/>
-      <c r="F462" s="28"/>
-      <c r="G462" s="28"/>
-      <c r="H462" s="28"/>
-      <c r="I462" s="28"/>
-      <c r="J462" s="28"/>
-      <c r="K462" s="28"/>
-      <c r="L462" s="28"/>
-    </row>
-    <row r="463" spans="1:12" s="29" customFormat="1">
-      <c r="A463" s="26"/>
-      <c r="B463" s="27"/>
-      <c r="C463" s="28"/>
-      <c r="D463" s="28"/>
-      <c r="E463" s="28"/>
-      <c r="F463" s="28"/>
-      <c r="G463" s="28"/>
-      <c r="H463" s="28"/>
-      <c r="I463" s="28"/>
-      <c r="J463" s="28"/>
-      <c r="K463" s="28"/>
-      <c r="L463" s="28"/>
-    </row>
-    <row r="464" spans="1:12" s="29" customFormat="1">
-      <c r="A464" s="26"/>
-      <c r="B464" s="27"/>
-      <c r="C464" s="28"/>
-      <c r="D464" s="28"/>
-      <c r="E464" s="28"/>
-      <c r="F464" s="28"/>
-      <c r="G464" s="28"/>
-      <c r="H464" s="28"/>
-      <c r="I464" s="28"/>
-      <c r="J464" s="28"/>
-      <c r="K464" s="28"/>
-      <c r="L464" s="28"/>
-    </row>
-    <row r="465" spans="1:12" s="29" customFormat="1">
-      <c r="A465" s="26"/>
-      <c r="B465" s="27"/>
-      <c r="C465" s="28"/>
-      <c r="D465" s="28"/>
-      <c r="E465" s="28"/>
-      <c r="F465" s="28"/>
-      <c r="G465" s="28"/>
-      <c r="H465" s="28"/>
-      <c r="I465" s="28"/>
-      <c r="J465" s="28"/>
-      <c r="K465" s="28"/>
-      <c r="L465" s="28"/>
-    </row>
-    <row r="466" spans="1:12" s="29" customFormat="1">
-      <c r="A466" s="26"/>
-      <c r="B466" s="27"/>
-      <c r="C466" s="28"/>
-      <c r="D466" s="28"/>
-      <c r="E466" s="28"/>
-      <c r="F466" s="28"/>
-      <c r="G466" s="28"/>
-      <c r="H466" s="28"/>
-      <c r="I466" s="28"/>
-      <c r="J466" s="28"/>
-      <c r="K466" s="28"/>
-      <c r="L466" s="28"/>
-    </row>
-    <row r="467" spans="1:12" s="29" customFormat="1">
-      <c r="A467" s="26"/>
-      <c r="B467" s="27"/>
-      <c r="C467" s="28"/>
-      <c r="D467" s="28"/>
-      <c r="E467" s="28"/>
-      <c r="F467" s="28"/>
-      <c r="G467" s="28"/>
-      <c r="H467" s="28"/>
-      <c r="I467" s="28"/>
-      <c r="J467" s="28"/>
-      <c r="K467" s="28"/>
-      <c r="L467" s="28"/>
-    </row>
-    <row r="468" spans="1:12" s="29" customFormat="1">
-      <c r="A468" s="26"/>
-      <c r="B468" s="27"/>
-      <c r="C468" s="28"/>
-      <c r="D468" s="28"/>
-      <c r="E468" s="28"/>
-      <c r="F468" s="28"/>
-      <c r="G468" s="28"/>
-      <c r="H468" s="28"/>
-      <c r="I468" s="28"/>
-      <c r="J468" s="28"/>
-      <c r="K468" s="28"/>
-      <c r="L468" s="28"/>
-    </row>
-    <row r="469" spans="1:12" s="29" customFormat="1">
-      <c r="A469" s="26"/>
-      <c r="B469" s="27"/>
-      <c r="C469" s="28"/>
-      <c r="D469" s="28"/>
-      <c r="E469" s="28"/>
-      <c r="F469" s="28"/>
-      <c r="G469" s="28"/>
-      <c r="H469" s="28"/>
-      <c r="I469" s="28"/>
-      <c r="J469" s="28"/>
-      <c r="K469" s="28"/>
-      <c r="L469" s="28"/>
-    </row>
-    <row r="470" spans="1:12" s="29" customFormat="1">
-      <c r="A470" s="26"/>
-      <c r="B470" s="27"/>
-      <c r="C470" s="28"/>
-      <c r="D470" s="28"/>
-      <c r="E470" s="28"/>
-      <c r="F470" s="28"/>
-      <c r="G470" s="28"/>
-      <c r="H470" s="28"/>
-      <c r="I470" s="28"/>
-      <c r="J470" s="28"/>
-      <c r="K470" s="28"/>
-      <c r="L470" s="28"/>
-    </row>
-    <row r="471" spans="1:12" s="29" customFormat="1">
-      <c r="A471" s="26"/>
-      <c r="B471" s="27"/>
-      <c r="C471" s="28"/>
-      <c r="D471" s="28"/>
-      <c r="E471" s="28"/>
-      <c r="F471" s="28"/>
-      <c r="G471" s="28"/>
-      <c r="H471" s="28"/>
-      <c r="I471" s="28"/>
-      <c r="J471" s="28"/>
-      <c r="K471" s="28"/>
-      <c r="L471" s="28"/>
-    </row>
-    <row r="472" spans="1:12" s="29" customFormat="1">
-      <c r="A472" s="26"/>
-      <c r="B472" s="27"/>
-      <c r="C472" s="28"/>
-      <c r="D472" s="28"/>
-      <c r="E472" s="28"/>
-      <c r="F472" s="28"/>
-      <c r="G472" s="28"/>
-      <c r="H472" s="28"/>
-      <c r="I472" s="28"/>
-      <c r="J472" s="28"/>
-      <c r="K472" s="28"/>
-      <c r="L472" s="28"/>
-    </row>
-    <row r="473" spans="1:12" s="29" customFormat="1">
-      <c r="A473" s="26"/>
-      <c r="B473" s="27"/>
-      <c r="C473" s="28"/>
-      <c r="D473" s="28"/>
-      <c r="E473" s="28"/>
-      <c r="F473" s="28"/>
-      <c r="G473" s="28"/>
-      <c r="H473" s="28"/>
-      <c r="I473" s="28"/>
-      <c r="J473" s="28"/>
-      <c r="K473" s="28"/>
-      <c r="L473" s="28"/>
-    </row>
-    <row r="474" spans="1:12" s="29" customFormat="1">
-      <c r="A474" s="26"/>
-      <c r="B474" s="27"/>
-      <c r="C474" s="28"/>
-      <c r="D474" s="28"/>
-      <c r="E474" s="28"/>
-      <c r="F474" s="28"/>
-      <c r="G474" s="28"/>
-      <c r="H474" s="28"/>
-      <c r="I474" s="28"/>
-      <c r="J474" s="28"/>
-      <c r="K474" s="28"/>
-      <c r="L474" s="28"/>
-    </row>
-    <row r="475" spans="1:12" s="29" customFormat="1">
-      <c r="A475" s="26"/>
-      <c r="B475" s="27"/>
-      <c r="C475" s="28"/>
-      <c r="D475" s="28"/>
-      <c r="E475" s="28"/>
-      <c r="F475" s="28"/>
-      <c r="G475" s="28"/>
-      <c r="H475" s="28"/>
-      <c r="I475" s="28"/>
-      <c r="J475" s="28"/>
-      <c r="K475" s="28"/>
-      <c r="L475" s="28"/>
-    </row>
-    <row r="476" spans="1:12" s="29" customFormat="1">
-      <c r="A476" s="26"/>
-      <c r="B476" s="27"/>
-      <c r="C476" s="28"/>
-      <c r="D476" s="28"/>
-      <c r="E476" s="28"/>
-      <c r="F476" s="28"/>
-      <c r="G476" s="28"/>
-      <c r="H476" s="28"/>
-      <c r="I476" s="28"/>
-      <c r="J476" s="28"/>
-      <c r="K476" s="28"/>
-      <c r="L476" s="28"/>
-    </row>
-    <row r="477" spans="1:12" s="29" customFormat="1">
-      <c r="A477" s="26"/>
-      <c r="B477" s="27"/>
-      <c r="C477" s="28"/>
-      <c r="D477" s="28"/>
-      <c r="E477" s="28"/>
-      <c r="F477" s="28"/>
-      <c r="G477" s="28"/>
-      <c r="H477" s="28"/>
-      <c r="I477" s="28"/>
-      <c r="J477" s="28"/>
-      <c r="K477" s="28"/>
-      <c r="L477" s="28"/>
-    </row>
-    <row r="478" spans="1:12" s="29" customFormat="1">
-      <c r="A478" s="26"/>
-      <c r="B478" s="27"/>
-      <c r="C478" s="28"/>
-      <c r="D478" s="28"/>
-      <c r="E478" s="28"/>
-      <c r="F478" s="28"/>
-      <c r="G478" s="28"/>
-      <c r="H478" s="28"/>
-      <c r="I478" s="28"/>
-      <c r="J478" s="28"/>
-      <c r="K478" s="28"/>
-      <c r="L478" s="28"/>
-    </row>
-    <row r="479" spans="1:12" s="29" customFormat="1">
-      <c r="A479" s="26"/>
-      <c r="B479" s="27"/>
-      <c r="C479" s="28"/>
-      <c r="D479" s="28"/>
-      <c r="E479" s="28"/>
-      <c r="F479" s="28"/>
-      <c r="G479" s="28"/>
-      <c r="H479" s="28"/>
-      <c r="I479" s="28"/>
-      <c r="J479" s="28"/>
-      <c r="K479" s="28"/>
-      <c r="L479" s="28"/>
-    </row>
-    <row r="480" spans="1:12" s="29" customFormat="1">
-      <c r="A480" s="26"/>
-      <c r="B480" s="27"/>
-      <c r="C480" s="28"/>
-      <c r="D480" s="28"/>
-      <c r="E480" s="28"/>
-      <c r="F480" s="28"/>
-      <c r="G480" s="28"/>
-      <c r="H480" s="28"/>
-      <c r="I480" s="28"/>
-      <c r="J480" s="28"/>
-      <c r="K480" s="28"/>
-      <c r="L480" s="28"/>
-    </row>
-    <row r="481" spans="1:12" s="29" customFormat="1">
-      <c r="A481" s="26"/>
-      <c r="B481" s="27"/>
-      <c r="C481" s="28"/>
-      <c r="D481" s="28"/>
-      <c r="E481" s="28"/>
-      <c r="F481" s="28"/>
-      <c r="G481" s="28"/>
-      <c r="H481" s="28"/>
-      <c r="I481" s="28"/>
-      <c r="J481" s="28"/>
-      <c r="K481" s="28"/>
-      <c r="L481" s="28"/>
-    </row>
-    <row r="482" spans="1:12" s="29" customFormat="1">
-      <c r="A482" s="26"/>
-      <c r="B482" s="27"/>
-      <c r="C482" s="28"/>
-      <c r="D482" s="28"/>
-      <c r="E482" s="28"/>
-      <c r="F482" s="28"/>
-      <c r="G482" s="28"/>
-      <c r="H482" s="28"/>
-      <c r="I482" s="28"/>
-      <c r="J482" s="28"/>
-      <c r="K482" s="28"/>
-      <c r="L482" s="28"/>
-    </row>
-    <row r="483" spans="1:12" s="29" customFormat="1">
-      <c r="A483" s="26"/>
-      <c r="B483" s="27"/>
-      <c r="C483" s="28"/>
-      <c r="D483" s="28"/>
-      <c r="E483" s="28"/>
-      <c r="F483" s="28"/>
-      <c r="G483" s="28"/>
-      <c r="H483" s="28"/>
-      <c r="I483" s="28"/>
-      <c r="J483" s="28"/>
-      <c r="K483" s="28"/>
-      <c r="L483" s="28"/>
-    </row>
-    <row r="484" spans="1:12" s="29" customFormat="1">
-      <c r="A484" s="26"/>
-      <c r="B484" s="27"/>
-      <c r="C484" s="28"/>
-      <c r="D484" s="28"/>
-      <c r="E484" s="28"/>
-      <c r="F484" s="28"/>
-      <c r="G484" s="28"/>
-      <c r="H484" s="28"/>
-      <c r="I484" s="28"/>
-      <c r="J484" s="28"/>
-      <c r="K484" s="28"/>
-      <c r="L484" s="28"/>
-    </row>
-    <row r="485" spans="1:12" s="29" customFormat="1">
-      <c r="A485" s="26"/>
-      <c r="B485" s="27"/>
-      <c r="C485" s="28"/>
-      <c r="D485" s="28"/>
-      <c r="E485" s="28"/>
-      <c r="F485" s="28"/>
-      <c r="G485" s="28"/>
-      <c r="H485" s="28"/>
-      <c r="I485" s="28"/>
-      <c r="J485" s="28"/>
-      <c r="K485" s="28"/>
-      <c r="L485" s="28"/>
-    </row>
-    <row r="486" spans="1:12" s="29" customFormat="1">
-      <c r="A486" s="26"/>
-      <c r="B486" s="27"/>
-      <c r="C486" s="28"/>
-      <c r="D486" s="28"/>
-      <c r="E486" s="28"/>
-      <c r="F486" s="28"/>
-      <c r="G486" s="28"/>
-      <c r="H486" s="28"/>
-      <c r="I486" s="28"/>
-      <c r="J486" s="28"/>
-      <c r="K486" s="28"/>
-      <c r="L486" s="28"/>
-    </row>
-    <row r="487" spans="1:12" s="29" customFormat="1">
-      <c r="A487" s="26"/>
-      <c r="B487" s="27"/>
-      <c r="C487" s="28"/>
-      <c r="D487" s="28"/>
-      <c r="E487" s="28"/>
-      <c r="F487" s="28"/>
-      <c r="G487" s="28"/>
-      <c r="H487" s="28"/>
-      <c r="I487" s="28"/>
-      <c r="J487" s="28"/>
-      <c r="K487" s="28"/>
-      <c r="L487" s="28"/>
-    </row>
-    <row r="488" spans="1:12" s="29" customFormat="1">
-      <c r="A488" s="26"/>
-      <c r="B488" s="27"/>
-      <c r="C488" s="28"/>
-      <c r="D488" s="28"/>
-      <c r="E488" s="28"/>
-      <c r="F488" s="28"/>
-      <c r="G488" s="28"/>
-      <c r="H488" s="28"/>
-      <c r="I488" s="28"/>
-      <c r="J488" s="28"/>
-      <c r="K488" s="28"/>
-      <c r="L488" s="28"/>
-    </row>
-    <row r="489" spans="1:12" s="29" customFormat="1">
-      <c r="A489" s="26"/>
-      <c r="B489" s="27"/>
-      <c r="C489" s="28"/>
-      <c r="D489" s="28"/>
-      <c r="E489" s="28"/>
-      <c r="F489" s="28"/>
-      <c r="G489" s="28"/>
-      <c r="H489" s="28"/>
-      <c r="I489" s="28"/>
-      <c r="J489" s="28"/>
-      <c r="K489" s="28"/>
-      <c r="L489" s="28"/>
-    </row>
-    <row r="490" spans="1:12" s="29" customFormat="1">
-      <c r="A490" s="26"/>
-      <c r="B490" s="27"/>
-      <c r="C490" s="28"/>
-      <c r="D490" s="28"/>
-      <c r="E490" s="28"/>
-      <c r="F490" s="28"/>
-      <c r="G490" s="28"/>
-      <c r="H490" s="28"/>
-      <c r="I490" s="28"/>
-      <c r="J490" s="28"/>
-      <c r="K490" s="28"/>
-      <c r="L490" s="28"/>
-    </row>
-    <row r="491" spans="1:12" s="29" customFormat="1">
-      <c r="A491" s="26"/>
-      <c r="B491" s="27"/>
-      <c r="C491" s="28"/>
-      <c r="D491" s="28"/>
-      <c r="E491" s="28"/>
-      <c r="F491" s="28"/>
-      <c r="G491" s="28"/>
-      <c r="H491" s="28"/>
-      <c r="I491" s="28"/>
-      <c r="J491" s="28"/>
-      <c r="K491" s="28"/>
-      <c r="L491" s="28"/>
-    </row>
-    <row r="492" spans="1:12" s="29" customFormat="1">
-      <c r="A492" s="26"/>
-      <c r="B492" s="27"/>
-      <c r="C492" s="28"/>
-      <c r="D492" s="28"/>
-      <c r="E492" s="28"/>
-      <c r="F492" s="28"/>
-      <c r="G492" s="28"/>
-      <c r="H492" s="28"/>
-      <c r="I492" s="28"/>
-      <c r="J492" s="28"/>
-      <c r="K492" s="28"/>
-      <c r="L492" s="28"/>
-    </row>
-    <row r="493" spans="1:12" s="29" customFormat="1">
-      <c r="A493" s="26"/>
-      <c r="B493" s="27"/>
-      <c r="C493" s="28"/>
-      <c r="D493" s="28"/>
-      <c r="E493" s="28"/>
-      <c r="F493" s="28"/>
-      <c r="G493" s="28"/>
-      <c r="H493" s="28"/>
-      <c r="I493" s="28"/>
-      <c r="J493" s="28"/>
-      <c r="K493" s="28"/>
-      <c r="L493" s="28"/>
-    </row>
-    <row r="494" spans="1:12" s="29" customFormat="1">
-      <c r="A494" s="26"/>
-      <c r="B494" s="27"/>
-      <c r="C494" s="28"/>
-      <c r="D494" s="28"/>
-      <c r="E494" s="28"/>
-      <c r="F494" s="28"/>
-      <c r="G494" s="28"/>
-      <c r="H494" s="28"/>
-      <c r="I494" s="28"/>
-      <c r="J494" s="28"/>
-      <c r="K494" s="28"/>
-      <c r="L494" s="28"/>
-    </row>
-    <row r="495" spans="1:12" s="29" customFormat="1">
-      <c r="A495" s="26"/>
-      <c r="B495" s="27"/>
-      <c r="C495" s="28"/>
-      <c r="D495" s="28"/>
-      <c r="E495" s="28"/>
-      <c r="F495" s="28"/>
-      <c r="G495" s="28"/>
-      <c r="H495" s="28"/>
-      <c r="I495" s="28"/>
-      <c r="J495" s="28"/>
-      <c r="K495" s="28"/>
-      <c r="L495" s="28"/>
-    </row>
-    <row r="496" spans="1:12" s="29" customFormat="1">
-      <c r="A496" s="26"/>
-      <c r="B496" s="27"/>
-      <c r="C496" s="28"/>
-      <c r="D496" s="28"/>
-      <c r="E496" s="28"/>
-      <c r="F496" s="28"/>
-      <c r="G496" s="28"/>
-      <c r="H496" s="28"/>
-      <c r="I496" s="28"/>
-      <c r="J496" s="28"/>
-      <c r="K496" s="28"/>
-      <c r="L496" s="28"/>
-    </row>
-    <row r="497" spans="1:12" s="29" customFormat="1">
-      <c r="A497" s="26"/>
-      <c r="B497" s="27"/>
-      <c r="C497" s="28"/>
-      <c r="D497" s="28"/>
-      <c r="E497" s="28"/>
-      <c r="F497" s="28"/>
-      <c r="G497" s="28"/>
-      <c r="H497" s="28"/>
-      <c r="I497" s="28"/>
-      <c r="J497" s="28"/>
-      <c r="K497" s="28"/>
-      <c r="L497" s="28"/>
-    </row>
-    <row r="498" spans="1:12" s="29" customFormat="1">
-      <c r="A498" s="26"/>
-      <c r="B498" s="27"/>
-      <c r="C498" s="28"/>
-      <c r="D498" s="28"/>
-      <c r="E498" s="28"/>
-      <c r="F498" s="28"/>
-      <c r="G498" s="28"/>
-      <c r="H498" s="28"/>
-      <c r="I498" s="28"/>
-      <c r="J498" s="28"/>
-      <c r="K498" s="28"/>
-      <c r="L498" s="28"/>
-    </row>
-    <row r="499" spans="1:12" s="29" customFormat="1">
-      <c r="A499" s="26"/>
-      <c r="B499" s="27"/>
-      <c r="C499" s="28"/>
-      <c r="D499" s="28"/>
-      <c r="E499" s="28"/>
-      <c r="F499" s="28"/>
-      <c r="G499" s="28"/>
-      <c r="H499" s="28"/>
-      <c r="I499" s="28"/>
-      <c r="J499" s="28"/>
-      <c r="K499" s="28"/>
-      <c r="L499" s="28"/>
-    </row>
-    <row r="500" spans="1:12" s="29" customFormat="1">
-      <c r="A500" s="26"/>
-      <c r="B500" s="27"/>
-      <c r="C500" s="28"/>
-      <c r="D500" s="28"/>
-      <c r="E500" s="28"/>
-      <c r="F500" s="28"/>
-      <c r="G500" s="28"/>
-      <c r="H500" s="28"/>
-      <c r="I500" s="28"/>
-      <c r="J500" s="28"/>
-      <c r="K500" s="28"/>
-      <c r="L500" s="28"/>
-    </row>
-    <row r="501" spans="1:12" s="29" customFormat="1">
-      <c r="A501" s="26"/>
-      <c r="B501" s="27"/>
-      <c r="C501" s="28"/>
-      <c r="D501" s="28"/>
-      <c r="E501" s="28"/>
-      <c r="F501" s="28"/>
-      <c r="G501" s="28"/>
-      <c r="H501" s="28"/>
-      <c r="I501" s="28"/>
-      <c r="J501" s="28"/>
-      <c r="K501" s="28"/>
-      <c r="L501" s="28"/>
-    </row>
-    <row r="502" spans="1:12" s="29" customFormat="1">
-      <c r="A502" s="26"/>
-      <c r="B502" s="27"/>
-      <c r="C502" s="28"/>
-      <c r="D502" s="28"/>
-      <c r="E502" s="28"/>
-      <c r="F502" s="28"/>
-      <c r="G502" s="28"/>
-      <c r="H502" s="28"/>
-      <c r="I502" s="28"/>
-      <c r="J502" s="28"/>
-      <c r="K502" s="28"/>
-      <c r="L502" s="28"/>
-    </row>
-    <row r="503" spans="1:12" s="29" customFormat="1">
-      <c r="A503" s="26"/>
-      <c r="B503" s="27"/>
-      <c r="C503" s="28"/>
-      <c r="D503" s="28"/>
-      <c r="E503" s="28"/>
-      <c r="F503" s="28"/>
-      <c r="G503" s="28"/>
-      <c r="H503" s="28"/>
-      <c r="I503" s="28"/>
-      <c r="J503" s="28"/>
-      <c r="K503" s="28"/>
-      <c r="L503" s="28"/>
-    </row>
-    <row r="504" spans="1:12" s="29" customFormat="1">
-      <c r="A504" s="26"/>
-      <c r="B504" s="27"/>
-      <c r="C504" s="28"/>
-      <c r="D504" s="28"/>
-      <c r="E504" s="28"/>
-      <c r="F504" s="28"/>
-      <c r="G504" s="28"/>
-      <c r="H504" s="28"/>
-      <c r="I504" s="28"/>
-      <c r="J504" s="28"/>
-      <c r="K504" s="28"/>
-      <c r="L504" s="28"/>
-    </row>
-    <row r="505" spans="1:12" s="29" customFormat="1"/>
-    <row r="506" spans="1:12" s="29" customFormat="1"/>
+    <row r="408" spans="1:12">
+      <c r="A408"/>
+      <c r="B408" s="22"/>
+      <c r="C408" s="13"/>
+      <c r="D408" s="13"/>
+      <c r="E408" s="13"/>
+      <c r="F408" s="13"/>
+      <c r="G408" s="13"/>
+      <c r="H408" s="13"/>
+      <c r="I408" s="13"/>
+      <c r="J408" s="13"/>
+      <c r="K408" s="13"/>
+      <c r="L408" s="13"/>
+    </row>
+    <row r="409" spans="1:12">
+      <c r="A409"/>
+      <c r="B409" s="22"/>
+      <c r="C409" s="13"/>
+      <c r="D409" s="13"/>
+      <c r="E409" s="13"/>
+      <c r="F409" s="13"/>
+      <c r="G409" s="13"/>
+      <c r="H409" s="13"/>
+      <c r="I409" s="13"/>
+      <c r="J409" s="13"/>
+      <c r="K409" s="13"/>
+      <c r="L409" s="13"/>
+    </row>
+    <row r="410" spans="1:12">
+      <c r="A410"/>
+      <c r="B410" s="22"/>
+      <c r="C410" s="13"/>
+      <c r="D410" s="13"/>
+      <c r="E410" s="13"/>
+      <c r="F410" s="13"/>
+      <c r="G410" s="13"/>
+      <c r="H410" s="13"/>
+      <c r="I410" s="13"/>
+      <c r="J410" s="13"/>
+      <c r="K410" s="13"/>
+      <c r="L410" s="13"/>
+    </row>
+    <row r="411" spans="1:12">
+      <c r="A411"/>
+      <c r="B411" s="22"/>
+      <c r="C411" s="13"/>
+      <c r="D411" s="13"/>
+      <c r="E411" s="13"/>
+      <c r="F411" s="13"/>
+      <c r="G411" s="13"/>
+      <c r="H411" s="13"/>
+      <c r="I411" s="13"/>
+      <c r="J411" s="13"/>
+      <c r="K411" s="13"/>
+      <c r="L411" s="13"/>
+    </row>
+    <row r="412" spans="1:12">
+      <c r="A412"/>
+      <c r="B412" s="22"/>
+      <c r="C412" s="13"/>
+      <c r="D412" s="13"/>
+      <c r="E412" s="13"/>
+      <c r="F412" s="13"/>
+      <c r="G412" s="13"/>
+      <c r="H412" s="13"/>
+      <c r="I412" s="13"/>
+      <c r="J412" s="13"/>
+      <c r="K412" s="13"/>
+      <c r="L412" s="13"/>
+    </row>
+    <row r="413" spans="1:12">
+      <c r="A413"/>
+      <c r="B413" s="22"/>
+      <c r="C413" s="13"/>
+      <c r="D413" s="13"/>
+      <c r="E413" s="13"/>
+      <c r="F413" s="13"/>
+      <c r="G413" s="13"/>
+      <c r="H413" s="13"/>
+      <c r="I413" s="13"/>
+      <c r="J413" s="13"/>
+      <c r="K413" s="13"/>
+      <c r="L413" s="13"/>
+    </row>
+    <row r="414" spans="1:12">
+      <c r="A414"/>
+      <c r="B414" s="22"/>
+      <c r="C414" s="13"/>
+      <c r="D414" s="13"/>
+      <c r="E414" s="13"/>
+      <c r="F414" s="13"/>
+      <c r="G414" s="13"/>
+      <c r="H414" s="13"/>
+      <c r="I414" s="13"/>
+      <c r="J414" s="13"/>
+      <c r="K414" s="13"/>
+      <c r="L414" s="13"/>
+    </row>
+    <row r="415" spans="1:12">
+      <c r="A415"/>
+      <c r="B415" s="22"/>
+      <c r="C415" s="13"/>
+      <c r="D415" s="13"/>
+      <c r="E415" s="13"/>
+      <c r="F415" s="13"/>
+      <c r="G415" s="13"/>
+      <c r="H415" s="13"/>
+      <c r="I415" s="13"/>
+      <c r="J415" s="13"/>
+      <c r="K415" s="13"/>
+      <c r="L415" s="13"/>
+    </row>
+    <row r="416" spans="1:12">
+      <c r="A416"/>
+      <c r="B416" s="22"/>
+      <c r="C416" s="13"/>
+      <c r="D416" s="13"/>
+      <c r="E416" s="13"/>
+      <c r="F416" s="13"/>
+      <c r="G416" s="13"/>
+      <c r="H416" s="13"/>
+      <c r="I416" s="13"/>
+      <c r="J416" s="13"/>
+      <c r="K416" s="13"/>
+      <c r="L416" s="13"/>
+    </row>
+    <row r="417" spans="1:12">
+      <c r="A417"/>
+      <c r="B417" s="22"/>
+      <c r="C417" s="13"/>
+      <c r="D417" s="13"/>
+      <c r="E417" s="13"/>
+      <c r="F417" s="13"/>
+      <c r="G417" s="13"/>
+      <c r="H417" s="13"/>
+      <c r="I417" s="13"/>
+      <c r="J417" s="13"/>
+      <c r="K417" s="13"/>
+      <c r="L417" s="13"/>
+    </row>
+    <row r="418" spans="1:12">
+      <c r="A418"/>
+      <c r="B418" s="22"/>
+      <c r="C418" s="13"/>
+      <c r="D418" s="13"/>
+      <c r="E418" s="13"/>
+      <c r="F418" s="13"/>
+      <c r="G418" s="13"/>
+      <c r="H418" s="13"/>
+      <c r="I418" s="13"/>
+      <c r="J418" s="13"/>
+      <c r="K418" s="13"/>
+      <c r="L418" s="13"/>
+    </row>
+    <row r="419" spans="1:12">
+      <c r="A419"/>
+      <c r="B419" s="22"/>
+      <c r="C419" s="13"/>
+      <c r="D419" s="13"/>
+      <c r="E419" s="13"/>
+      <c r="F419" s="13"/>
+      <c r="G419" s="13"/>
+      <c r="H419" s="13"/>
+      <c r="I419" s="13"/>
+      <c r="J419" s="13"/>
+      <c r="K419" s="13"/>
+      <c r="L419" s="13"/>
+    </row>
+    <row r="420" spans="1:12">
+      <c r="A420"/>
+      <c r="B420" s="22"/>
+      <c r="C420" s="13"/>
+      <c r="D420" s="13"/>
+      <c r="E420" s="13"/>
+      <c r="F420" s="13"/>
+      <c r="G420" s="13"/>
+      <c r="H420" s="13"/>
+      <c r="I420" s="13"/>
+      <c r="J420" s="13"/>
+      <c r="K420" s="13"/>
+      <c r="L420" s="13"/>
+    </row>
+    <row r="421" spans="1:12">
+      <c r="A421"/>
+      <c r="B421" s="22"/>
+      <c r="C421" s="13"/>
+      <c r="D421" s="13"/>
+      <c r="E421" s="13"/>
+      <c r="F421" s="13"/>
+      <c r="G421" s="13"/>
+      <c r="H421" s="13"/>
+      <c r="I421" s="13"/>
+      <c r="J421" s="13"/>
+      <c r="K421" s="13"/>
+      <c r="L421" s="13"/>
+    </row>
+    <row r="422" spans="1:12">
+      <c r="A422"/>
+      <c r="B422" s="22"/>
+      <c r="C422" s="13"/>
+      <c r="D422" s="13"/>
+      <c r="E422" s="13"/>
+      <c r="F422" s="13"/>
+      <c r="G422" s="13"/>
+      <c r="H422" s="13"/>
+      <c r="I422" s="13"/>
+      <c r="J422" s="13"/>
+      <c r="K422" s="13"/>
+      <c r="L422" s="13"/>
+    </row>
+    <row r="423" spans="1:12">
+      <c r="A423"/>
+      <c r="B423" s="22"/>
+      <c r="C423" s="13"/>
+      <c r="D423" s="13"/>
+      <c r="E423" s="13"/>
+      <c r="F423" s="13"/>
+      <c r="G423" s="13"/>
+      <c r="H423" s="13"/>
+      <c r="I423" s="13"/>
+      <c r="J423" s="13"/>
+      <c r="K423" s="13"/>
+      <c r="L423" s="13"/>
+    </row>
+    <row r="424" spans="1:12">
+      <c r="A424"/>
+      <c r="B424" s="22"/>
+      <c r="C424" s="13"/>
+      <c r="D424" s="13"/>
+      <c r="E424" s="13"/>
+      <c r="F424" s="13"/>
+      <c r="G424" s="13"/>
+      <c r="H424" s="13"/>
+      <c r="I424" s="13"/>
+      <c r="J424" s="13"/>
+      <c r="K424" s="13"/>
+      <c r="L424" s="13"/>
+    </row>
+    <row r="425" spans="1:12">
+      <c r="A425"/>
+      <c r="B425" s="22"/>
+      <c r="C425" s="13"/>
+      <c r="D425" s="13"/>
+      <c r="E425" s="13"/>
+      <c r="F425" s="13"/>
+      <c r="G425" s="13"/>
+      <c r="H425" s="13"/>
+      <c r="I425" s="13"/>
+      <c r="J425" s="13"/>
+      <c r="K425" s="13"/>
+      <c r="L425" s="13"/>
+    </row>
+    <row r="426" spans="1:12">
+      <c r="A426"/>
+      <c r="B426" s="22"/>
+      <c r="C426" s="13"/>
+      <c r="D426" s="13"/>
+      <c r="E426" s="13"/>
+      <c r="F426" s="13"/>
+      <c r="G426" s="13"/>
+      <c r="H426" s="13"/>
+      <c r="I426" s="13"/>
+      <c r="J426" s="13"/>
+      <c r="K426" s="13"/>
+      <c r="L426" s="13"/>
+    </row>
+    <row r="427" spans="1:12">
+      <c r="A427"/>
+      <c r="B427" s="22"/>
+      <c r="C427" s="13"/>
+      <c r="D427" s="13"/>
+      <c r="E427" s="13"/>
+      <c r="F427" s="13"/>
+      <c r="G427" s="13"/>
+      <c r="H427" s="13"/>
+      <c r="I427" s="13"/>
+      <c r="J427" s="13"/>
+      <c r="K427" s="13"/>
+      <c r="L427" s="13"/>
+    </row>
+    <row r="428" spans="1:12">
+      <c r="A428"/>
+      <c r="B428" s="22"/>
+      <c r="C428" s="13"/>
+      <c r="D428" s="13"/>
+      <c r="E428" s="13"/>
+      <c r="F428" s="13"/>
+      <c r="G428" s="13"/>
+      <c r="H428" s="13"/>
+      <c r="I428" s="13"/>
+      <c r="J428" s="13"/>
+      <c r="K428" s="13"/>
+      <c r="L428" s="13"/>
+    </row>
+    <row r="429" spans="1:12">
+      <c r="A429"/>
+      <c r="B429" s="22"/>
+      <c r="C429" s="13"/>
+      <c r="D429" s="13"/>
+      <c r="E429" s="13"/>
+      <c r="F429" s="13"/>
+      <c r="G429" s="13"/>
+      <c r="H429" s="13"/>
+      <c r="I429" s="13"/>
+      <c r="J429" s="13"/>
+      <c r="K429" s="13"/>
+      <c r="L429" s="13"/>
+    </row>
+    <row r="430" spans="1:12">
+      <c r="A430"/>
+      <c r="B430" s="22"/>
+      <c r="C430" s="13"/>
+      <c r="D430" s="13"/>
+      <c r="E430" s="13"/>
+      <c r="F430" s="13"/>
+      <c r="G430" s="13"/>
+      <c r="H430" s="13"/>
+      <c r="I430" s="13"/>
+      <c r="J430" s="13"/>
+      <c r="K430" s="13"/>
+      <c r="L430" s="13"/>
+    </row>
+    <row r="431" spans="1:12">
+      <c r="A431"/>
+      <c r="B431" s="22"/>
+      <c r="C431" s="13"/>
+      <c r="D431" s="13"/>
+      <c r="E431" s="13"/>
+      <c r="F431" s="13"/>
+      <c r="G431" s="13"/>
+      <c r="H431" s="13"/>
+      <c r="I431" s="13"/>
+      <c r="J431" s="13"/>
+      <c r="K431" s="13"/>
+      <c r="L431" s="13"/>
+    </row>
+    <row r="432" spans="1:12">
+      <c r="A432"/>
+      <c r="B432" s="22"/>
+      <c r="C432" s="13"/>
+      <c r="D432" s="13"/>
+      <c r="E432" s="13"/>
+      <c r="F432" s="13"/>
+      <c r="G432" s="13"/>
+      <c r="H432" s="13"/>
+      <c r="I432" s="13"/>
+      <c r="J432" s="13"/>
+      <c r="K432" s="13"/>
+      <c r="L432" s="13"/>
+    </row>
+    <row r="433" spans="1:12">
+      <c r="A433"/>
+      <c r="B433" s="22"/>
+      <c r="C433" s="13"/>
+      <c r="D433" s="13"/>
+      <c r="E433" s="13"/>
+      <c r="F433" s="13"/>
+      <c r="G433" s="13"/>
+      <c r="H433" s="13"/>
+      <c r="I433" s="13"/>
+      <c r="J433" s="13"/>
+      <c r="K433" s="13"/>
+      <c r="L433" s="13"/>
+    </row>
+    <row r="434" spans="1:12">
+      <c r="A434"/>
+      <c r="B434" s="22"/>
+      <c r="C434" s="13"/>
+      <c r="D434" s="13"/>
+      <c r="E434" s="13"/>
+      <c r="F434" s="13"/>
+      <c r="G434" s="13"/>
+      <c r="H434" s="13"/>
+      <c r="I434" s="13"/>
+      <c r="J434" s="13"/>
+      <c r="K434" s="13"/>
+      <c r="L434" s="13"/>
+    </row>
+    <row r="435" spans="1:12">
+      <c r="A435"/>
+      <c r="B435" s="22"/>
+      <c r="C435" s="13"/>
+      <c r="D435" s="13"/>
+      <c r="E435" s="13"/>
+      <c r="F435" s="13"/>
+      <c r="G435" s="13"/>
+      <c r="H435" s="13"/>
+      <c r="I435" s="13"/>
+      <c r="J435" s="13"/>
+      <c r="K435" s="13"/>
+      <c r="L435" s="13"/>
+    </row>
+    <row r="436" spans="1:12">
+      <c r="A436"/>
+      <c r="B436" s="22"/>
+      <c r="C436" s="13"/>
+      <c r="D436" s="13"/>
+      <c r="E436" s="13"/>
+      <c r="F436" s="13"/>
+      <c r="G436" s="13"/>
+      <c r="H436" s="13"/>
+      <c r="I436" s="13"/>
+      <c r="J436" s="13"/>
+      <c r="K436" s="13"/>
+      <c r="L436" s="13"/>
+    </row>
+    <row r="437" spans="1:12">
+      <c r="A437"/>
+      <c r="B437" s="22"/>
+      <c r="C437" s="13"/>
+      <c r="D437" s="13"/>
+      <c r="E437" s="13"/>
+      <c r="F437" s="13"/>
+      <c r="G437" s="13"/>
+      <c r="H437" s="13"/>
+      <c r="I437" s="13"/>
+      <c r="J437" s="13"/>
+      <c r="K437" s="13"/>
+      <c r="L437" s="13"/>
+    </row>
+    <row r="438" spans="1:12">
+      <c r="A438"/>
+      <c r="B438" s="22"/>
+      <c r="C438" s="13"/>
+      <c r="D438" s="13"/>
+      <c r="E438" s="13"/>
+      <c r="F438" s="13"/>
+      <c r="G438" s="13"/>
+      <c r="H438" s="13"/>
+      <c r="I438" s="13"/>
+      <c r="J438" s="13"/>
+      <c r="K438" s="13"/>
+      <c r="L438" s="13"/>
+    </row>
+    <row r="439" spans="1:12">
+      <c r="A439"/>
+      <c r="B439" s="22"/>
+      <c r="C439" s="13"/>
+      <c r="D439" s="13"/>
+      <c r="E439" s="13"/>
+      <c r="F439" s="13"/>
+      <c r="G439" s="13"/>
+      <c r="H439" s="13"/>
+      <c r="I439" s="13"/>
+      <c r="J439" s="13"/>
+      <c r="K439" s="13"/>
+      <c r="L439" s="13"/>
+    </row>
+    <row r="440" spans="1:12">
+      <c r="A440"/>
+      <c r="B440" s="22"/>
+      <c r="C440" s="13"/>
+      <c r="D440" s="13"/>
+      <c r="E440" s="13"/>
+      <c r="F440" s="13"/>
+      <c r="G440" s="13"/>
+      <c r="H440" s="13"/>
+      <c r="I440" s="13"/>
+      <c r="J440" s="13"/>
+      <c r="K440" s="13"/>
+      <c r="L440" s="13"/>
+    </row>
+    <row r="441" spans="1:12">
+      <c r="A441"/>
+      <c r="B441" s="22"/>
+      <c r="C441" s="13"/>
+      <c r="D441" s="13"/>
+      <c r="E441" s="13"/>
+      <c r="F441" s="13"/>
+      <c r="G441" s="13"/>
+      <c r="H441" s="13"/>
+      <c r="I441" s="13"/>
+      <c r="J441" s="13"/>
+      <c r="K441" s="13"/>
+      <c r="L441" s="13"/>
+    </row>
+    <row r="442" spans="1:12">
+      <c r="A442"/>
+      <c r="B442" s="22"/>
+      <c r="C442" s="13"/>
+      <c r="D442" s="13"/>
+      <c r="E442" s="13"/>
+      <c r="F442" s="13"/>
+      <c r="G442" s="13"/>
+      <c r="H442" s="13"/>
+      <c r="I442" s="13"/>
+      <c r="J442" s="13"/>
+      <c r="K442" s="13"/>
+      <c r="L442" s="13"/>
+    </row>
+    <row r="443" spans="1:12">
+      <c r="A443"/>
+      <c r="B443" s="22"/>
+      <c r="C443" s="13"/>
+      <c r="D443" s="13"/>
+      <c r="E443" s="13"/>
+      <c r="F443" s="13"/>
+      <c r="G443" s="13"/>
+      <c r="H443" s="13"/>
+      <c r="I443" s="13"/>
+      <c r="J443" s="13"/>
+      <c r="K443" s="13"/>
+      <c r="L443" s="13"/>
+    </row>
+    <row r="444" spans="1:12">
+      <c r="A444"/>
+      <c r="B444" s="22"/>
+      <c r="C444" s="13"/>
+      <c r="D444" s="13"/>
+      <c r="E444" s="13"/>
+      <c r="F444" s="13"/>
+      <c r="G444" s="13"/>
+      <c r="H444" s="13"/>
+      <c r="I444" s="13"/>
+      <c r="J444" s="13"/>
+      <c r="K444" s="13"/>
+      <c r="L444" s="13"/>
+    </row>
+    <row r="445" spans="1:12">
+      <c r="A445"/>
+      <c r="B445" s="22"/>
+      <c r="C445" s="13"/>
+      <c r="D445" s="13"/>
+      <c r="E445" s="13"/>
+      <c r="F445" s="13"/>
+      <c r="G445" s="13"/>
+      <c r="H445" s="13"/>
+      <c r="I445" s="13"/>
+      <c r="J445" s="13"/>
+      <c r="K445" s="13"/>
+      <c r="L445" s="13"/>
+    </row>
+    <row r="446" spans="1:12">
+      <c r="A446"/>
+      <c r="B446" s="22"/>
+      <c r="C446" s="13"/>
+      <c r="D446" s="13"/>
+      <c r="E446" s="13"/>
+      <c r="F446" s="13"/>
+      <c r="G446" s="13"/>
+      <c r="H446" s="13"/>
+      <c r="I446" s="13"/>
+      <c r="J446" s="13"/>
+      <c r="K446" s="13"/>
+      <c r="L446" s="13"/>
+    </row>
+    <row r="447" spans="1:12">
+      <c r="A447"/>
+      <c r="B447" s="22"/>
+      <c r="C447" s="13"/>
+      <c r="D447" s="13"/>
+      <c r="E447" s="13"/>
+      <c r="F447" s="13"/>
+      <c r="G447" s="13"/>
+      <c r="H447" s="13"/>
+      <c r="I447" s="13"/>
+      <c r="J447" s="13"/>
+      <c r="K447" s="13"/>
+      <c r="L447" s="13"/>
+    </row>
+    <row r="448" spans="1:12">
+      <c r="A448"/>
+      <c r="B448" s="22"/>
+      <c r="C448" s="13"/>
+      <c r="D448" s="13"/>
+      <c r="E448" s="13"/>
+      <c r="F448" s="13"/>
+      <c r="G448" s="13"/>
+      <c r="H448" s="13"/>
+      <c r="I448" s="13"/>
+      <c r="J448" s="13"/>
+      <c r="K448" s="13"/>
+      <c r="L448" s="13"/>
+    </row>
+    <row r="449" spans="1:12">
+      <c r="A449"/>
+      <c r="B449" s="22"/>
+      <c r="C449" s="13"/>
+      <c r="D449" s="13"/>
+      <c r="E449" s="13"/>
+      <c r="F449" s="13"/>
+      <c r="G449" s="13"/>
+      <c r="H449" s="13"/>
+      <c r="I449" s="13"/>
+      <c r="J449" s="13"/>
+      <c r="K449" s="13"/>
+      <c r="L449" s="13"/>
+    </row>
+    <row r="450" spans="1:12">
+      <c r="A450"/>
+      <c r="B450" s="22"/>
+      <c r="C450" s="13"/>
+      <c r="D450" s="13"/>
+      <c r="E450" s="13"/>
+      <c r="F450" s="13"/>
+      <c r="G450" s="13"/>
+      <c r="H450" s="13"/>
+      <c r="I450" s="13"/>
+      <c r="J450" s="13"/>
+      <c r="K450" s="13"/>
+      <c r="L450" s="13"/>
+    </row>
+    <row r="451" spans="1:12">
+      <c r="A451"/>
+      <c r="B451" s="22"/>
+      <c r="C451" s="13"/>
+      <c r="D451" s="13"/>
+      <c r="E451" s="13"/>
+      <c r="F451" s="13"/>
+      <c r="G451" s="13"/>
+      <c r="H451" s="13"/>
+      <c r="I451" s="13"/>
+      <c r="J451" s="13"/>
+      <c r="K451" s="13"/>
+      <c r="L451" s="13"/>
+    </row>
+    <row r="452" spans="1:12">
+      <c r="A452"/>
+      <c r="B452" s="22"/>
+      <c r="C452" s="13"/>
+      <c r="D452" s="13"/>
+      <c r="E452" s="13"/>
+      <c r="F452" s="13"/>
+      <c r="G452" s="13"/>
+      <c r="H452" s="13"/>
+      <c r="I452" s="13"/>
+      <c r="J452" s="13"/>
+      <c r="K452" s="13"/>
+      <c r="L452" s="13"/>
+    </row>
+    <row r="453" spans="1:12">
+      <c r="A453"/>
+      <c r="B453" s="22"/>
+      <c r="C453" s="13"/>
+      <c r="D453" s="13"/>
+      <c r="E453" s="13"/>
+      <c r="F453" s="13"/>
+      <c r="G453" s="13"/>
+      <c r="H453" s="13"/>
+      <c r="I453" s="13"/>
+      <c r="J453" s="13"/>
+      <c r="K453" s="13"/>
+      <c r="L453" s="13"/>
+    </row>
+    <row r="454" spans="1:12">
+      <c r="A454"/>
+      <c r="B454" s="22"/>
+      <c r="C454" s="13"/>
+      <c r="D454" s="13"/>
+      <c r="E454" s="13"/>
+      <c r="F454" s="13"/>
+      <c r="G454" s="13"/>
+      <c r="H454" s="13"/>
+      <c r="I454" s="13"/>
+      <c r="J454" s="13"/>
+      <c r="K454" s="13"/>
+      <c r="L454" s="13"/>
+    </row>
+    <row r="455" spans="1:12">
+      <c r="A455"/>
+      <c r="B455" s="22"/>
+      <c r="C455" s="13"/>
+      <c r="D455" s="13"/>
+      <c r="E455" s="13"/>
+      <c r="F455" s="13"/>
+      <c r="G455" s="13"/>
+      <c r="H455" s="13"/>
+      <c r="I455" s="13"/>
+      <c r="J455" s="13"/>
+      <c r="K455" s="13"/>
+      <c r="L455" s="13"/>
+    </row>
+    <row r="456" spans="1:12">
+      <c r="A456"/>
+      <c r="B456" s="22"/>
+      <c r="C456" s="13"/>
+      <c r="D456" s="13"/>
+      <c r="E456" s="13"/>
+      <c r="F456" s="13"/>
+      <c r="G456" s="13"/>
+      <c r="H456" s="13"/>
+      <c r="I456" s="13"/>
+      <c r="J456" s="13"/>
+      <c r="K456" s="13"/>
+      <c r="L456" s="13"/>
+    </row>
+    <row r="457" spans="1:12">
+      <c r="A457"/>
+      <c r="B457" s="22"/>
+      <c r="C457" s="13"/>
+      <c r="D457" s="13"/>
+      <c r="E457" s="13"/>
+      <c r="F457" s="13"/>
+      <c r="G457" s="13"/>
+      <c r="H457" s="13"/>
+      <c r="I457" s="13"/>
+      <c r="J457" s="13"/>
+      <c r="K457" s="13"/>
+      <c r="L457" s="13"/>
+    </row>
+    <row r="458" spans="1:12">
+      <c r="A458"/>
+      <c r="B458" s="22"/>
+      <c r="C458" s="13"/>
+      <c r="D458" s="13"/>
+      <c r="E458" s="13"/>
+      <c r="F458" s="13"/>
+      <c r="G458" s="13"/>
+      <c r="H458" s="13"/>
+      <c r="I458" s="13"/>
+      <c r="J458" s="13"/>
+      <c r="K458" s="13"/>
+      <c r="L458" s="13"/>
+    </row>
+    <row r="459" spans="1:12">
+      <c r="A459"/>
+      <c r="B459" s="22"/>
+      <c r="C459" s="13"/>
+      <c r="D459" s="13"/>
+      <c r="E459" s="13"/>
+      <c r="F459" s="13"/>
+      <c r="G459" s="13"/>
+      <c r="H459" s="13"/>
+      <c r="I459" s="13"/>
+      <c r="J459" s="13"/>
+      <c r="K459" s="13"/>
+      <c r="L459" s="13"/>
+    </row>
+    <row r="460" spans="1:12">
+      <c r="A460"/>
+      <c r="B460" s="22"/>
+      <c r="C460" s="13"/>
+      <c r="D460" s="13"/>
+      <c r="E460" s="13"/>
+      <c r="F460" s="13"/>
+      <c r="G460" s="13"/>
+      <c r="H460" s="13"/>
+      <c r="I460" s="13"/>
+      <c r="J460" s="13"/>
+      <c r="K460" s="13"/>
+      <c r="L460" s="13"/>
+    </row>
+    <row r="461" spans="1:12">
+      <c r="A461"/>
+      <c r="B461" s="22"/>
+      <c r="C461" s="13"/>
+      <c r="D461" s="13"/>
+      <c r="E461" s="13"/>
+      <c r="F461" s="13"/>
+      <c r="G461" s="13"/>
+      <c r="H461" s="13"/>
+      <c r="I461" s="13"/>
+      <c r="J461" s="13"/>
+      <c r="K461" s="13"/>
+      <c r="L461" s="13"/>
+    </row>
+    <row r="462" spans="1:12">
+      <c r="A462"/>
+      <c r="B462" s="22"/>
+      <c r="C462" s="13"/>
+      <c r="D462" s="13"/>
+      <c r="E462" s="13"/>
+      <c r="F462" s="13"/>
+      <c r="G462" s="13"/>
+      <c r="H462" s="13"/>
+      <c r="I462" s="13"/>
+      <c r="J462" s="13"/>
+      <c r="K462" s="13"/>
+      <c r="L462" s="13"/>
+    </row>
+    <row r="463" spans="1:12">
+      <c r="A463"/>
+      <c r="B463" s="22"/>
+      <c r="C463" s="13"/>
+      <c r="D463" s="13"/>
+      <c r="E463" s="13"/>
+      <c r="F463" s="13"/>
+      <c r="G463" s="13"/>
+      <c r="H463" s="13"/>
+      <c r="I463" s="13"/>
+      <c r="J463" s="13"/>
+      <c r="K463" s="13"/>
+      <c r="L463" s="13"/>
+    </row>
+    <row r="464" spans="1:12">
+      <c r="A464"/>
+      <c r="B464" s="22"/>
+      <c r="C464" s="13"/>
+      <c r="D464" s="13"/>
+      <c r="E464" s="13"/>
+      <c r="F464" s="13"/>
+      <c r="G464" s="13"/>
+      <c r="H464" s="13"/>
+      <c r="I464" s="13"/>
+      <c r="J464" s="13"/>
+      <c r="K464" s="13"/>
+      <c r="L464" s="13"/>
+    </row>
+    <row r="465" spans="1:12">
+      <c r="A465"/>
+      <c r="B465" s="22"/>
+      <c r="C465" s="13"/>
+      <c r="D465" s="13"/>
+      <c r="E465" s="13"/>
+      <c r="F465" s="13"/>
+      <c r="G465" s="13"/>
+      <c r="H465" s="13"/>
+      <c r="I465" s="13"/>
+      <c r="J465" s="13"/>
+      <c r="K465" s="13"/>
+      <c r="L465" s="13"/>
+    </row>
+    <row r="466" spans="1:12">
+      <c r="A466"/>
+      <c r="B466" s="22"/>
+      <c r="C466" s="13"/>
+      <c r="D466" s="13"/>
+      <c r="E466" s="13"/>
+      <c r="F466" s="13"/>
+      <c r="G466" s="13"/>
+      <c r="H466" s="13"/>
+      <c r="I466" s="13"/>
+      <c r="J466" s="13"/>
+      <c r="K466" s="13"/>
+      <c r="L466" s="13"/>
+    </row>
+    <row r="467" spans="1:12">
+      <c r="A467"/>
+      <c r="B467" s="22"/>
+      <c r="C467" s="13"/>
+      <c r="D467" s="13"/>
+      <c r="E467" s="13"/>
+      <c r="F467" s="13"/>
+      <c r="G467" s="13"/>
+      <c r="H467" s="13"/>
+      <c r="I467" s="13"/>
+      <c r="J467" s="13"/>
+      <c r="K467" s="13"/>
+      <c r="L467" s="13"/>
+    </row>
+    <row r="468" spans="1:12">
+      <c r="A468"/>
+      <c r="B468" s="22"/>
+      <c r="C468" s="13"/>
+      <c r="D468" s="13"/>
+      <c r="E468" s="13"/>
+      <c r="F468" s="13"/>
+      <c r="G468" s="13"/>
+      <c r="H468" s="13"/>
+      <c r="I468" s="13"/>
+      <c r="J468" s="13"/>
+      <c r="K468" s="13"/>
+      <c r="L468" s="13"/>
+    </row>
+    <row r="469" spans="1:12">
+      <c r="A469"/>
+      <c r="B469" s="22"/>
+      <c r="C469" s="13"/>
+      <c r="D469" s="13"/>
+      <c r="E469" s="13"/>
+      <c r="F469" s="13"/>
+      <c r="G469" s="13"/>
+      <c r="H469" s="13"/>
+      <c r="I469" s="13"/>
+      <c r="J469" s="13"/>
+      <c r="K469" s="13"/>
+      <c r="L469" s="13"/>
+    </row>
+    <row r="470" spans="1:12">
+      <c r="A470"/>
+      <c r="B470" s="22"/>
+      <c r="C470" s="13"/>
+      <c r="D470" s="13"/>
+      <c r="E470" s="13"/>
+      <c r="F470" s="13"/>
+      <c r="G470" s="13"/>
+      <c r="H470" s="13"/>
+      <c r="I470" s="13"/>
+      <c r="J470" s="13"/>
+      <c r="K470" s="13"/>
+      <c r="L470" s="13"/>
+    </row>
+    <row r="471" spans="1:12">
+      <c r="A471"/>
+      <c r="B471" s="22"/>
+      <c r="C471" s="13"/>
+      <c r="D471" s="13"/>
+      <c r="E471" s="13"/>
+      <c r="F471" s="13"/>
+      <c r="G471" s="13"/>
+      <c r="H471" s="13"/>
+      <c r="I471" s="13"/>
+      <c r="J471" s="13"/>
+      <c r="K471" s="13"/>
+      <c r="L471" s="13"/>
+    </row>
+    <row r="472" spans="1:12">
+      <c r="A472"/>
+      <c r="B472" s="22"/>
+      <c r="C472" s="13"/>
+      <c r="D472" s="13"/>
+      <c r="E472" s="13"/>
+      <c r="F472" s="13"/>
+      <c r="G472" s="13"/>
+      <c r="H472" s="13"/>
+      <c r="I472" s="13"/>
+      <c r="J472" s="13"/>
+      <c r="K472" s="13"/>
+      <c r="L472" s="13"/>
+    </row>
+    <row r="473" spans="1:12">
+      <c r="A473"/>
+      <c r="B473" s="22"/>
+      <c r="C473" s="13"/>
+      <c r="D473" s="13"/>
+      <c r="E473" s="13"/>
+      <c r="F473" s="13"/>
+      <c r="G473" s="13"/>
+      <c r="H473" s="13"/>
+      <c r="I473" s="13"/>
+      <c r="J473" s="13"/>
+      <c r="K473" s="13"/>
+      <c r="L473" s="13"/>
+    </row>
+    <row r="474" spans="1:12">
+      <c r="A474"/>
+      <c r="B474" s="22"/>
+      <c r="C474" s="13"/>
+      <c r="D474" s="13"/>
+      <c r="E474" s="13"/>
+      <c r="F474" s="13"/>
+      <c r="G474" s="13"/>
+      <c r="H474" s="13"/>
+      <c r="I474" s="13"/>
+      <c r="J474" s="13"/>
+      <c r="K474" s="13"/>
+      <c r="L474" s="13"/>
+    </row>
+    <row r="475" spans="1:12">
+      <c r="A475"/>
+      <c r="B475" s="22"/>
+      <c r="C475" s="13"/>
+      <c r="D475" s="13"/>
+      <c r="E475" s="13"/>
+      <c r="F475" s="13"/>
+      <c r="G475" s="13"/>
+      <c r="H475" s="13"/>
+      <c r="I475" s="13"/>
+      <c r="J475" s="13"/>
+      <c r="K475" s="13"/>
+      <c r="L475" s="13"/>
+    </row>
+    <row r="476" spans="1:12">
+      <c r="A476"/>
+      <c r="B476" s="22"/>
+      <c r="C476" s="13"/>
+      <c r="D476" s="13"/>
+      <c r="E476" s="13"/>
+      <c r="F476" s="13"/>
+      <c r="G476" s="13"/>
+      <c r="H476" s="13"/>
+      <c r="I476" s="13"/>
+      <c r="J476" s="13"/>
+      <c r="K476" s="13"/>
+      <c r="L476" s="13"/>
+    </row>
+    <row r="477" spans="1:12">
+      <c r="A477"/>
+      <c r="B477" s="22"/>
+      <c r="C477" s="13"/>
+      <c r="D477" s="13"/>
+      <c r="E477" s="13"/>
+      <c r="F477" s="13"/>
+      <c r="G477" s="13"/>
+      <c r="H477" s="13"/>
+      <c r="I477" s="13"/>
+      <c r="J477" s="13"/>
+      <c r="K477" s="13"/>
+      <c r="L477" s="13"/>
+    </row>
+    <row r="478" spans="1:12">
+      <c r="A478"/>
+      <c r="B478" s="22"/>
+      <c r="C478" s="13"/>
+      <c r="D478" s="13"/>
+      <c r="E478" s="13"/>
+      <c r="F478" s="13"/>
+      <c r="G478" s="13"/>
+      <c r="H478" s="13"/>
+      <c r="I478" s="13"/>
+      <c r="J478" s="13"/>
+      <c r="K478" s="13"/>
+      <c r="L478" s="13"/>
+    </row>
+    <row r="479" spans="1:12">
+      <c r="A479"/>
+      <c r="B479" s="22"/>
+      <c r="C479" s="13"/>
+      <c r="D479" s="13"/>
+      <c r="E479" s="13"/>
+      <c r="F479" s="13"/>
+      <c r="G479" s="13"/>
+      <c r="H479" s="13"/>
+      <c r="I479" s="13"/>
+      <c r="J479" s="13"/>
+      <c r="K479" s="13"/>
+      <c r="L479" s="13"/>
+    </row>
+    <row r="480" spans="1:12">
+      <c r="A480"/>
+      <c r="B480" s="22"/>
+      <c r="C480" s="13"/>
+      <c r="D480" s="13"/>
+      <c r="E480" s="13"/>
+      <c r="F480" s="13"/>
+      <c r="G480" s="13"/>
+      <c r="H480" s="13"/>
+      <c r="I480" s="13"/>
+      <c r="J480" s="13"/>
+      <c r="K480" s="13"/>
+      <c r="L480" s="13"/>
+    </row>
+    <row r="481" spans="1:12">
+      <c r="A481"/>
+      <c r="B481" s="22"/>
+      <c r="C481" s="13"/>
+      <c r="D481" s="13"/>
+      <c r="E481" s="13"/>
+      <c r="F481" s="13"/>
+      <c r="G481" s="13"/>
+      <c r="H481" s="13"/>
+      <c r="I481" s="13"/>
+      <c r="J481" s="13"/>
+      <c r="K481" s="13"/>
+      <c r="L481" s="13"/>
+    </row>
+    <row r="482" spans="1:12">
+      <c r="A482"/>
+      <c r="B482" s="22"/>
+      <c r="C482" s="13"/>
+      <c r="D482" s="13"/>
+      <c r="E482" s="13"/>
+      <c r="F482" s="13"/>
+      <c r="G482" s="13"/>
+      <c r="H482" s="13"/>
+      <c r="I482" s="13"/>
+      <c r="J482" s="13"/>
+      <c r="K482" s="13"/>
+      <c r="L482" s="13"/>
+    </row>
+    <row r="483" spans="1:12">
+      <c r="A483"/>
+      <c r="B483" s="22"/>
+      <c r="C483" s="13"/>
+      <c r="D483" s="13"/>
+      <c r="E483" s="13"/>
+      <c r="F483" s="13"/>
+      <c r="G483" s="13"/>
+      <c r="H483" s="13"/>
+      <c r="I483" s="13"/>
+      <c r="J483" s="13"/>
+      <c r="K483" s="13"/>
+      <c r="L483" s="13"/>
+    </row>
+    <row r="484" spans="1:12">
+      <c r="A484"/>
+      <c r="B484" s="22"/>
+      <c r="C484" s="13"/>
+      <c r="D484" s="13"/>
+      <c r="E484" s="13"/>
+      <c r="F484" s="13"/>
+      <c r="G484" s="13"/>
+      <c r="H484" s="13"/>
+      <c r="I484" s="13"/>
+      <c r="J484" s="13"/>
+      <c r="K484" s="13"/>
+      <c r="L484" s="13"/>
+    </row>
+    <row r="485" spans="1:12">
+      <c r="A485"/>
+      <c r="B485" s="22"/>
+      <c r="C485" s="13"/>
+      <c r="D485" s="13"/>
+      <c r="E485" s="13"/>
+      <c r="F485" s="13"/>
+      <c r="G485" s="13"/>
+      <c r="H485" s="13"/>
+      <c r="I485" s="13"/>
+      <c r="J485" s="13"/>
+      <c r="K485" s="13"/>
+      <c r="L485" s="13"/>
+    </row>
+    <row r="486" spans="1:12">
+      <c r="A486"/>
+      <c r="B486" s="22"/>
+      <c r="C486" s="13"/>
+      <c r="D486" s="13"/>
+      <c r="E486" s="13"/>
+      <c r="F486" s="13"/>
+      <c r="G486" s="13"/>
+      <c r="H486" s="13"/>
+      <c r="I486" s="13"/>
+      <c r="J486" s="13"/>
+      <c r="K486" s="13"/>
+      <c r="L486" s="13"/>
+    </row>
+    <row r="487" spans="1:12">
+      <c r="A487"/>
+      <c r="B487" s="22"/>
+      <c r="C487" s="13"/>
+      <c r="D487" s="13"/>
+      <c r="E487" s="13"/>
+      <c r="F487" s="13"/>
+      <c r="G487" s="13"/>
+      <c r="H487" s="13"/>
+      <c r="I487" s="13"/>
+      <c r="J487" s="13"/>
+      <c r="K487" s="13"/>
+      <c r="L487" s="13"/>
+    </row>
+    <row r="488" spans="1:12">
+      <c r="A488"/>
+      <c r="B488" s="22"/>
+      <c r="C488" s="13"/>
+      <c r="D488" s="13"/>
+      <c r="E488" s="13"/>
+      <c r="F488" s="13"/>
+      <c r="G488" s="13"/>
+      <c r="H488" s="13"/>
+      <c r="I488" s="13"/>
+      <c r="J488" s="13"/>
+      <c r="K488" s="13"/>
+      <c r="L488" s="13"/>
+    </row>
+    <row r="489" spans="1:12">
+      <c r="A489"/>
+      <c r="B489" s="22"/>
+      <c r="C489" s="13"/>
+      <c r="D489" s="13"/>
+      <c r="E489" s="13"/>
+      <c r="F489" s="13"/>
+      <c r="G489" s="13"/>
+      <c r="H489" s="13"/>
+      <c r="I489" s="13"/>
+      <c r="J489" s="13"/>
+      <c r="K489" s="13"/>
+      <c r="L489" s="13"/>
+    </row>
+    <row r="490" spans="1:12">
+      <c r="A490"/>
+      <c r="B490" s="22"/>
+      <c r="C490" s="13"/>
+      <c r="D490" s="13"/>
+      <c r="E490" s="13"/>
+      <c r="F490" s="13"/>
+      <c r="G490" s="13"/>
+      <c r="H490" s="13"/>
+      <c r="I490" s="13"/>
+      <c r="J490" s="13"/>
+      <c r="K490" s="13"/>
+      <c r="L490" s="13"/>
+    </row>
+    <row r="491" spans="1:12">
+      <c r="A491"/>
+      <c r="B491" s="22"/>
+      <c r="C491" s="13"/>
+      <c r="D491" s="13"/>
+      <c r="E491" s="13"/>
+      <c r="F491" s="13"/>
+      <c r="G491" s="13"/>
+      <c r="H491" s="13"/>
+      <c r="I491" s="13"/>
+      <c r="J491" s="13"/>
+      <c r="K491" s="13"/>
+      <c r="L491" s="13"/>
+    </row>
+    <row r="492" spans="1:12">
+      <c r="A492"/>
+      <c r="B492" s="22"/>
+      <c r="C492" s="13"/>
+      <c r="D492" s="13"/>
+      <c r="E492" s="13"/>
+      <c r="F492" s="13"/>
+      <c r="G492" s="13"/>
+      <c r="H492" s="13"/>
+      <c r="I492" s="13"/>
+      <c r="J492" s="13"/>
+      <c r="K492" s="13"/>
+      <c r="L492" s="13"/>
+    </row>
+    <row r="493" spans="1:12">
+      <c r="A493"/>
+      <c r="B493" s="22"/>
+      <c r="C493" s="13"/>
+      <c r="D493" s="13"/>
+      <c r="E493" s="13"/>
+      <c r="F493" s="13"/>
+      <c r="G493" s="13"/>
+      <c r="H493" s="13"/>
+      <c r="I493" s="13"/>
+      <c r="J493" s="13"/>
+      <c r="K493" s="13"/>
+      <c r="L493" s="13"/>
+    </row>
+    <row r="494" spans="1:12">
+      <c r="A494"/>
+      <c r="B494" s="22"/>
+      <c r="C494" s="13"/>
+      <c r="D494" s="13"/>
+      <c r="E494" s="13"/>
+      <c r="F494" s="13"/>
+      <c r="G494" s="13"/>
+      <c r="H494" s="13"/>
+      <c r="I494" s="13"/>
+      <c r="J494" s="13"/>
+      <c r="K494" s="13"/>
+      <c r="L494" s="13"/>
+    </row>
+    <row r="495" spans="1:12">
+      <c r="A495"/>
+      <c r="B495" s="22"/>
+      <c r="C495" s="13"/>
+      <c r="D495" s="13"/>
+      <c r="E495" s="13"/>
+      <c r="F495" s="13"/>
+      <c r="G495" s="13"/>
+      <c r="H495" s="13"/>
+      <c r="I495" s="13"/>
+      <c r="J495" s="13"/>
+      <c r="K495" s="13"/>
+      <c r="L495" s="13"/>
+    </row>
+    <row r="496" spans="1:12">
+      <c r="A496"/>
+      <c r="B496" s="22"/>
+      <c r="C496" s="13"/>
+      <c r="D496" s="13"/>
+      <c r="E496" s="13"/>
+      <c r="F496" s="13"/>
+      <c r="G496" s="13"/>
+      <c r="H496" s="13"/>
+      <c r="I496" s="13"/>
+      <c r="J496" s="13"/>
+      <c r="K496" s="13"/>
+      <c r="L496" s="13"/>
+    </row>
+    <row r="497" spans="1:12">
+      <c r="A497"/>
+      <c r="B497" s="22"/>
+      <c r="C497" s="13"/>
+      <c r="D497" s="13"/>
+      <c r="E497" s="13"/>
+      <c r="F497" s="13"/>
+      <c r="G497" s="13"/>
+      <c r="H497" s="13"/>
+      <c r="I497" s="13"/>
+      <c r="J497" s="13"/>
+      <c r="K497" s="13"/>
+      <c r="L497" s="13"/>
+    </row>
+    <row r="498" spans="1:12">
+      <c r="A498"/>
+      <c r="B498" s="22"/>
+      <c r="C498" s="13"/>
+      <c r="D498" s="13"/>
+      <c r="E498" s="13"/>
+      <c r="F498" s="13"/>
+      <c r="G498" s="13"/>
+      <c r="H498" s="13"/>
+      <c r="I498" s="13"/>
+      <c r="J498" s="13"/>
+      <c r="K498" s="13"/>
+      <c r="L498" s="13"/>
+    </row>
+    <row r="499" spans="1:12">
+      <c r="A499"/>
+      <c r="B499" s="22"/>
+      <c r="C499" s="13"/>
+      <c r="D499" s="13"/>
+      <c r="E499" s="13"/>
+      <c r="F499" s="13"/>
+      <c r="G499" s="13"/>
+      <c r="H499" s="13"/>
+      <c r="I499" s="13"/>
+      <c r="J499" s="13"/>
+      <c r="K499" s="13"/>
+      <c r="L499" s="13"/>
+    </row>
+    <row r="500" spans="1:12">
+      <c r="A500"/>
+      <c r="B500" s="22"/>
+      <c r="C500" s="13"/>
+      <c r="D500" s="13"/>
+      <c r="E500" s="13"/>
+      <c r="F500" s="13"/>
+      <c r="G500" s="13"/>
+      <c r="H500" s="13"/>
+      <c r="I500" s="13"/>
+      <c r="J500" s="13"/>
+      <c r="K500" s="13"/>
+      <c r="L500" s="13"/>
+    </row>
+    <row r="501" spans="1:12">
+      <c r="A501"/>
+      <c r="B501" s="22"/>
+      <c r="C501" s="13"/>
+      <c r="D501" s="13"/>
+      <c r="E501" s="13"/>
+      <c r="F501" s="13"/>
+      <c r="G501" s="13"/>
+      <c r="H501" s="13"/>
+      <c r="I501" s="13"/>
+      <c r="J501" s="13"/>
+      <c r="K501" s="13"/>
+      <c r="L501" s="13"/>
+    </row>
+    <row r="502" spans="1:12">
+      <c r="A502"/>
+      <c r="B502" s="22"/>
+      <c r="C502" s="13"/>
+      <c r="D502" s="13"/>
+      <c r="E502" s="13"/>
+      <c r="F502" s="13"/>
+      <c r="G502" s="13"/>
+      <c r="H502" s="13"/>
+      <c r="I502" s="13"/>
+      <c r="J502" s="13"/>
+      <c r="K502" s="13"/>
+      <c r="L502" s="13"/>
+    </row>
+    <row r="503" spans="1:12">
+      <c r="A503"/>
+      <c r="B503" s="22"/>
+      <c r="C503" s="13"/>
+      <c r="D503" s="13"/>
+      <c r="E503" s="13"/>
+      <c r="F503" s="13"/>
+      <c r="G503" s="13"/>
+      <c r="H503" s="13"/>
+      <c r="I503" s="13"/>
+      <c r="J503" s="13"/>
+      <c r="K503" s="13"/>
+      <c r="L503" s="13"/>
+    </row>
+    <row r="504" spans="1:12">
+      <c r="A504"/>
+      <c r="B504" s="22"/>
+      <c r="C504" s="13"/>
+      <c r="D504" s="13"/>
+      <c r="E504" s="13"/>
+      <c r="F504" s="13"/>
+      <c r="G504" s="13"/>
+      <c r="H504" s="13"/>
+      <c r="I504" s="13"/>
+      <c r="J504" s="13"/>
+      <c r="K504" s="13"/>
+      <c r="L504" s="13"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup scale="39" fitToHeight="10" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup scale="41" fitToHeight="10" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>